--- a/outputs/daily/hr_rankings_2026-08-06.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-06.xlsx
@@ -1287,12 +1287,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>592518</t>
+          <t>665487</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Manny Machado</t>
+          <t>Fernando Tatis</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1336,7 +1336,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>61.9</v>
+        <v>62.4</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>50.9</v>
+        <v>50.2</v>
       </c>
       <c r="Q4" t="n">
         <v>86.09999999999999</v>
@@ -1363,13 +1363,13 @@
         <v>28.2</v>
       </c>
       <c r="S4" t="n">
-        <v>92.09999999999999</v>
+        <v>88.7</v>
       </c>
       <c r="T4" t="n">
         <v>78</v>
       </c>
       <c r="U4" t="n">
-        <v>6</v>
+        <v>29.2</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1425,22 +1425,22 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/25, 0 HR</t>
+          <t>Last 7 games: 5/26, 1 HR</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1450,72 +1450,72 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>EV profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>11.43</t>
+          <t>10.58</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>46.53</t>
+          <t>52.43</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>91.29</t>
+          <t>92.46</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>101.9072</t>
+          <t>104.2761</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.4495</t>
+          <t>0.4516</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.203</t>
+          <t>0.1708</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.3347</t>
+          <t>0.3574</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>74.64</t>
+          <t>75.44</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>44.51</t>
+          <t>57.35</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>40.92</t>
+          <t>33.68</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>28.99</t>
+          <t>21.31</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.2067</t>
+          <t>0.1346</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>664034</t>
+          <t>592518</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ty France</t>
+          <t>Manny Machado</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1593,7 +1593,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1612,7 +1612,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>61.4</v>
+        <v>61.8</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>45.7</v>
+        <v>50.9</v>
       </c>
       <c r="Q5" t="n">
         <v>86.09999999999999</v>
@@ -1639,13 +1639,13 @@
         <v>28.2</v>
       </c>
       <c r="S5" t="n">
-        <v>90.40000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T5" t="n">
         <v>78</v>
       </c>
       <c r="U5" t="n">
-        <v>34.2</v>
+        <v>5.1</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1701,12 +1701,12 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Contact streak: 8/23 over last 7 games</t>
+          <t>Last 7 games: 4/26, 0 HR</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1731,67 +1731,67 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>10.01</t>
+          <t>11.43</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>48.61</t>
+          <t>46.53</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>91.67</t>
+          <t>91.29</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>101.4652</t>
+          <t>101.9072</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.439</t>
+          <t>0.4495</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.1828</t>
+          <t>0.203</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.3315</t>
+          <t>0.3347</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>74.64</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>18.76</t>
+          <t>44.51</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>36.15</t>
+          <t>40.92</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>24.27</t>
+          <t>28.99</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.1947</t>
+          <t>0.2067</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>665487</t>
+          <t>664034</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Fernando Tatis</t>
+          <t>Ty France</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1869,7 +1869,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1906,7 +1906,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>50.2</v>
+        <v>45.7</v>
       </c>
       <c r="Q6" t="n">
         <v>86.09999999999999</v>
@@ -1915,13 +1915,13 @@
         <v>28.2</v>
       </c>
       <c r="S6" t="n">
-        <v>88.7</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T6" t="n">
         <v>78</v>
       </c>
       <c r="U6" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1977,12 +1977,12 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 0 HR</t>
+          <t>Contact streak: 8/25 over last 7 games</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -2002,72 +2002,72 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>EV profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>10.58</t>
+          <t>10.01</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>52.43</t>
+          <t>48.61</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>92.46</t>
+          <t>91.67</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>104.2761</t>
+          <t>101.4652</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.4516</t>
+          <t>0.439</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.1708</t>
+          <t>0.1828</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3574</t>
+          <t>0.3315</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>75.44</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>57.35</t>
+          <t>18.76</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>33.68</t>
+          <t>36.15</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>21.31</t>
+          <t>24.27</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.1346</t>
+          <t>0.1947</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -2992,7 +2992,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>58.9</v>
+        <v>58.8</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3025,7 +3025,7 @@
         <v>50</v>
       </c>
       <c r="U10" t="n">
-        <v>46.5</v>
+        <v>44.8</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/26, 1 HR</t>
+          <t>Last 7 games: 8/27, 1 HR</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
@@ -6304,7 +6304,7 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>54.2</v>
+        <v>54.1</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
@@ -6337,7 +6337,7 @@
         <v>80</v>
       </c>
       <c r="U22" t="n">
-        <v>25.3</v>
+        <v>23.4</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
@@ -6398,7 +6398,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
@@ -6408,7 +6408,7 @@
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 1 HR</t>
+          <t>Last 7 games: 4/26, 1 HR</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
@@ -7684,7 +7684,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>52.8</v>
+        <v>52.7</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -7717,7 +7717,7 @@
         <v>50</v>
       </c>
       <c r="U27" t="n">
-        <v>81.7</v>
+        <v>80</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
@@ -7778,7 +7778,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
@@ -8187,27 +8187,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>593428</t>
+          <t>671739</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Xander Bogaerts</t>
+          <t>Michael Harris</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-08-07T01:40:00Z</t>
+          <t>2026-08-06T23:15:00Z</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -8217,26 +8217,26 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Kohl Drake</t>
+          <t>Janson Junk</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>684442</t>
+          <t>676083</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>52.4</v>
+        <v>52.3</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
@@ -8250,26 +8250,26 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Projected Lineup, Pitcher Vulnerable, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>26.8</v>
+        <v>48.7</v>
       </c>
       <c r="Q29" t="n">
-        <v>86.09999999999999</v>
+        <v>42.5</v>
       </c>
       <c r="R29" t="n">
-        <v>28.2</v>
+        <v>30.9</v>
       </c>
       <c r="S29" t="n">
-        <v>71.7</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T29" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U29" t="n">
-        <v>32</v>
+        <v>30.3</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -8308,7 +8308,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr"/>
@@ -8325,134 +8325,134 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Contact streak: 7/21 over last 7 games</t>
+          <t>Last 7 games: 5/25, 1 HR</t>
         </is>
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 15.0% barrel, 3.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.5% barrel, 10.1 HR allowed</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>6.06</t>
+          <t>10.92</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>39.41</t>
+          <t>47.46</t>
         </is>
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>88.58</t>
+          <t>90.69</t>
         </is>
       </c>
       <c r="AQ29" t="inlineStr">
         <is>
-          <t>99.8411</t>
+          <t>103.5282</t>
         </is>
       </c>
       <c r="AR29" t="inlineStr">
         <is>
-          <t>0.3822</t>
+          <t>0.4786</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr">
         <is>
-          <t>0.1313</t>
+          <t>0.1928</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.3409</t>
         </is>
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>72.31</t>
+          <t>74.72</t>
         </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>27.66</t>
+          <t>47.75</t>
         </is>
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>43.87</t>
+          <t>36.22</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>23.34</t>
+          <t>23.12</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>0.1091</t>
+          <t>0.1894</t>
         </is>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>7.52</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>42.82</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>90.55</t>
         </is>
       </c>
       <c r="BD29" t="inlineStr">
         <is>
-          <t>0.594</t>
+          <t>0.4194</t>
         </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
-          <t>0.295</t>
+          <t>0.1599</t>
         </is>
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>23.57</t>
         </is>
       </c>
       <c r="BG29" t="inlineStr"/>
       <c r="BH29" t="inlineStr"/>
       <c r="BI29" t="inlineStr">
         <is>
-          <t>Chase Field</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ29" t="inlineStr"/>
@@ -8463,27 +8463,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>671739</t>
+          <t>593428</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Michael Harris</t>
+          <t>Xander Bogaerts</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-08-06T23:15:00Z</t>
+          <t>2026-08-07T01:40:00Z</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -8493,22 +8493,22 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Janson Junk</t>
+          <t>Kohl Drake</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>676083</t>
+          <t>684442</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L30" t="n">
@@ -8526,26 +8526,26 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Pitcher Vulnerable, Platoon Edge</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>48.7</v>
+        <v>26.8</v>
       </c>
       <c r="Q30" t="n">
-        <v>42.5</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="R30" t="n">
-        <v>30.9</v>
+        <v>28.2</v>
       </c>
       <c r="S30" t="n">
-        <v>90.40000000000001</v>
+        <v>71.7</v>
       </c>
       <c r="T30" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U30" t="n">
-        <v>30.3</v>
+        <v>29.7</v>
       </c>
       <c r="V30" t="inlineStr">
         <is>
@@ -8559,7 +8559,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
@@ -8584,7 +8584,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr"/>
@@ -8601,134 +8601,134 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 1 HR</t>
+          <t>Last 7 games: 7/22, 0 HR</t>
         </is>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.5% barrel, 10.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 15.0% barrel, 3.0 HR allowed</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>10.92</t>
+          <t>6.06</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>47.46</t>
+          <t>39.41</t>
         </is>
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>90.69</t>
+          <t>88.58</t>
         </is>
       </c>
       <c r="AQ30" t="inlineStr">
         <is>
-          <t>103.5282</t>
+          <t>99.8411</t>
         </is>
       </c>
       <c r="AR30" t="inlineStr">
         <is>
-          <t>0.4786</t>
+          <t>0.3822</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr">
         <is>
-          <t>0.1928</t>
+          <t>0.1313</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr">
         <is>
-          <t>0.3409</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>74.72</t>
+          <t>72.31</t>
         </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
-          <t>47.75</t>
+          <t>27.66</t>
         </is>
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>36.22</t>
+          <t>43.87</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>23.12</t>
+          <t>23.34</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>0.1894</t>
+          <t>0.1091</t>
         </is>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>7.52</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>42.82</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
         <is>
-          <t>90.55</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="BD30" t="inlineStr">
         <is>
-          <t>0.4194</t>
+          <t>0.594</t>
         </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
-          <t>0.1599</t>
+          <t>0.295</t>
         </is>
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>23.57</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="BG30" t="inlineStr"/>
       <c r="BH30" t="inlineStr"/>
       <c r="BI30" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Chase Field</t>
         </is>
       </c>
       <c r="BJ30" t="inlineStr"/>
@@ -9291,27 +9291,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>650859</t>
+          <t>641933</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Luis Rengifo</t>
+          <t>Tyler O'Neill</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-07T01:40:00Z</t>
+          <t>2026-08-06T16:35:00Z</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -9321,26 +9321,26 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Kohl Drake</t>
+          <t>Ryan Johnson</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>684442</t>
+          <t>696270</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>51.8</v>
+        <v>51.7</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
@@ -9354,26 +9354,26 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Projected Lineup, Pitcher Vulnerable, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>17.2</v>
+        <v>47.4</v>
       </c>
       <c r="Q33" t="n">
-        <v>85.8</v>
+        <v>44.2</v>
       </c>
       <c r="R33" t="n">
-        <v>28.2</v>
+        <v>32.1</v>
       </c>
       <c r="S33" t="n">
-        <v>95.5</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T33" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U33" t="n">
-        <v>22.9</v>
+        <v>70.3</v>
       </c>
       <c r="V33" t="inlineStr">
         <is>
@@ -9387,7 +9387,7 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
@@ -9412,7 +9412,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD33" t="inlineStr"/>
@@ -9429,134 +9429,134 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/22, 0 HR</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 15.0% barrel, 3.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.3% barrel, 9.6 HR allowed</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>fly-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>11.04</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>35.43</t>
+          <t>42.32</t>
         </is>
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>87.87</t>
+          <t>89.71</t>
         </is>
       </c>
       <c r="AQ33" t="inlineStr">
         <is>
-          <t>98.1275</t>
+          <t>100.5246</t>
         </is>
       </c>
       <c r="AR33" t="inlineStr">
         <is>
-          <t>0.3568</t>
+          <t>0.4285</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr">
         <is>
-          <t>0.0996</t>
+          <t>0.2107</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr">
         <is>
-          <t>0.3076</t>
+          <t>0.318</t>
         </is>
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>70.76</t>
+          <t>72.81</t>
         </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>15.35</t>
+          <t>24.03</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>37.11</t>
+          <t>47.54</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>17.03</t>
+          <t>39.07</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>0.0781</t>
+          <t>0.1804</t>
         </is>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>9.27</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>35.93</t>
         </is>
       </c>
       <c r="BC33" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>87.33</t>
         </is>
       </c>
       <c r="BD33" t="inlineStr">
         <is>
-          <t>0.594</t>
+          <t>0.4472</t>
         </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
-          <t>0.295</t>
+          <t>0.1868</t>
         </is>
       </c>
       <c r="BF33" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>32.34</t>
         </is>
       </c>
       <c r="BG33" t="inlineStr"/>
       <c r="BH33" t="inlineStr"/>
       <c r="BI33" t="inlineStr">
         <is>
-          <t>Chase Field</t>
+          <t>Oriole Park at Camden Yards</t>
         </is>
       </c>
       <c r="BJ33" t="inlineStr"/>
@@ -9567,27 +9567,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>641933</t>
+          <t>650859</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Tyler O'Neill</t>
+          <t>Luis Rengifo</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-08-06T16:35:00Z</t>
+          <t>2026-08-07T01:40:00Z</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -9597,22 +9597,22 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Ryan Johnson</t>
+          <t>Kohl Drake</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>696270</t>
+          <t>684442</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L34" t="n">
@@ -9630,26 +9630,26 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Pitcher Vulnerable, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>47.4</v>
+        <v>17.2</v>
       </c>
       <c r="Q34" t="n">
-        <v>44.2</v>
+        <v>85.8</v>
       </c>
       <c r="R34" t="n">
-        <v>32.1</v>
+        <v>28.2</v>
       </c>
       <c r="S34" t="n">
-        <v>90.40000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="T34" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U34" t="n">
-        <v>70.3</v>
+        <v>21.1</v>
       </c>
       <c r="V34" t="inlineStr">
         <is>
@@ -9663,7 +9663,7 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
@@ -9688,7 +9688,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD34" t="inlineStr"/>
@@ -9705,134 +9705,134 @@
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Last 7 games: 6/23, 0 HR</t>
         </is>
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.3% barrel, 9.6 HR allowed</t>
+          <t>switch hitter; pitcher baseline 15.0% barrel, 3.0 HR allowed</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>42.32</t>
+          <t>35.43</t>
         </is>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>89.71</t>
+          <t>87.87</t>
         </is>
       </c>
       <c r="AQ34" t="inlineStr">
         <is>
-          <t>100.5246</t>
+          <t>98.1275</t>
         </is>
       </c>
       <c r="AR34" t="inlineStr">
         <is>
-          <t>0.4285</t>
+          <t>0.3568</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr">
         <is>
-          <t>0.2107</t>
+          <t>0.0996</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr">
         <is>
-          <t>0.318</t>
+          <t>0.3076</t>
         </is>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>72.81</t>
+          <t>70.76</t>
         </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>24.03</t>
+          <t>15.35</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>47.54</t>
+          <t>37.11</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>39.07</t>
+          <t>17.03</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>0.1804</t>
+          <t>0.0781</t>
         </is>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>9.27</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>35.93</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
         <is>
-          <t>87.33</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="BD34" t="inlineStr">
         <is>
-          <t>0.4472</t>
+          <t>0.594</t>
         </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
-          <t>0.1868</t>
+          <t>0.295</t>
         </is>
       </c>
       <c r="BF34" t="inlineStr">
         <is>
-          <t>32.34</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="BG34" t="inlineStr"/>
       <c r="BH34" t="inlineStr"/>
       <c r="BI34" t="inlineStr">
         <is>
-          <t>Oriole Park at Camden Yards</t>
+          <t>Chase Field</t>
         </is>
       </c>
       <c r="BJ34" t="inlineStr"/>
@@ -9843,27 +9843,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>687749</t>
+          <t>596019</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Jase Bowen</t>
+          <t>Francisco Lindor</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-07T01:40:00Z</t>
+          <t>2026-08-06T17:10:00Z</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -9873,17 +9873,17 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Kohl Drake</t>
+          <t>Foster Griffin</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>684442</t>
+          <t>656492</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -9892,7 +9892,7 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>51.3</v>
+        <v>51.1</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
@@ -9906,26 +9906,26 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Pitcher Vulnerable, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="Q35" t="n">
-        <v>86.09999999999999</v>
+        <v>40.2</v>
       </c>
       <c r="R35" t="n">
-        <v>28.2</v>
+        <v>27.6</v>
       </c>
       <c r="S35" t="n">
-        <v>40.2</v>
+        <v>95.5</v>
       </c>
       <c r="T35" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="U35" t="n">
-        <v>30.3</v>
+        <v>33.7</v>
       </c>
       <c r="V35" t="inlineStr">
         <is>
@@ -9939,7 +9939,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
@@ -9964,7 +9964,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>H:2026 P:2026</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD35" t="inlineStr"/>
@@ -9981,12 +9981,12 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
@@ -9996,119 +9996,119 @@
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/15, 1 HR</t>
+          <t>Last 7 games: 6/27, 1 HR</t>
         </is>
       </c>
       <c r="AL35" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 15.0% barrel, 3.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.2% barrel, 19.0 HR allowed</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>9.46</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>35.7</t>
+          <t>47.34</t>
         </is>
       </c>
       <c r="AP35" t="inlineStr">
         <is>
+          <t>91.2</t>
+        </is>
+      </c>
+      <c r="AQ35" t="inlineStr">
+        <is>
+          <t>100.371</t>
+        </is>
+      </c>
+      <c r="AR35" t="inlineStr">
+        <is>
+          <t>0.4596</t>
+        </is>
+      </c>
+      <c r="AS35" t="inlineStr">
+        <is>
+          <t>0.2003</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr">
+        <is>
+          <t>0.3485</t>
+        </is>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
+          <t>72.09</t>
+        </is>
+      </c>
+      <c r="AV35" t="inlineStr">
+        <is>
+          <t>22.74</t>
+        </is>
+      </c>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>43.85</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>29.88</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>15.6</t>
+        </is>
+      </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>0.1906</t>
+        </is>
+      </c>
+      <c r="BA35" t="inlineStr">
+        <is>
+          <t>9.2</t>
+        </is>
+      </c>
+      <c r="BB35" t="inlineStr">
+        <is>
+          <t>37.6</t>
+        </is>
+      </c>
+      <c r="BC35" t="inlineStr">
+        <is>
           <t>87.9</t>
         </is>
       </c>
-      <c r="AQ35" t="inlineStr">
-        <is>
-          <t>99.7068</t>
-        </is>
-      </c>
-      <c r="AR35" t="inlineStr">
-        <is>
-          <t>0.368</t>
-        </is>
-      </c>
-      <c r="AS35" t="inlineStr">
-        <is>
-          <t>0.148</t>
-        </is>
-      </c>
-      <c r="AT35" t="inlineStr">
-        <is>
-          <t>0.276</t>
-        </is>
-      </c>
-      <c r="AU35" t="inlineStr">
-        <is>
-          <t>73.6</t>
-        </is>
-      </c>
-      <c r="AV35" t="inlineStr">
-        <is>
-          <t>32.0</t>
-        </is>
-      </c>
-      <c r="AW35" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>33.3</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>0.073</t>
-        </is>
-      </c>
-      <c r="BA35" t="inlineStr">
-        <is>
-          <t>15.0</t>
-        </is>
-      </c>
-      <c r="BB35" t="inlineStr">
-        <is>
-          <t>52.5</t>
-        </is>
-      </c>
-      <c r="BC35" t="inlineStr">
-        <is>
-          <t>91.7</t>
-        </is>
-      </c>
       <c r="BD35" t="inlineStr">
         <is>
-          <t>0.594</t>
+          <t>0.411</t>
         </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
-          <t>0.295</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="BF35" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="BG35" t="inlineStr"/>
       <c r="BH35" t="inlineStr"/>
       <c r="BI35" t="inlineStr">
         <is>
-          <t>Chase Field</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BJ35" t="inlineStr"/>
@@ -10119,27 +10119,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>596019</t>
+          <t>607208</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Francisco Lindor</t>
+          <t>Trea Turner</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-06T17:10:00Z</t>
+          <t>2026-08-06T22:05:00Z</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -10154,17 +10154,17 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Foster Griffin</t>
+          <t>Miles Mikolas</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>656492</t>
+          <t>571945</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L36" t="n">
@@ -10182,26 +10182,26 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>47</v>
+        <v>28.9</v>
       </c>
       <c r="Q36" t="n">
-        <v>40.2</v>
+        <v>61.4</v>
       </c>
       <c r="R36" t="n">
-        <v>27.6</v>
+        <v>34.3</v>
       </c>
       <c r="S36" t="n">
         <v>95.5</v>
       </c>
       <c r="T36" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U36" t="n">
-        <v>33.7</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="V36" t="inlineStr">
         <is>
@@ -10240,7 +10240,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD36" t="inlineStr"/>
@@ -10257,27 +10257,27 @@
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL36" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.2% barrel, 19.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.5% barrel, 26.9 HR allowed</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
@@ -10287,104 +10287,104 @@
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>9.46</t>
+          <t>6.36</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>47.34</t>
+          <t>41.54</t>
         </is>
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>91.2</t>
+          <t>88.95</t>
         </is>
       </c>
       <c r="AQ36" t="inlineStr">
         <is>
-          <t>100.371</t>
+          <t>99.574</t>
         </is>
       </c>
       <c r="AR36" t="inlineStr">
         <is>
-          <t>0.4596</t>
+          <t>0.3918</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr">
         <is>
-          <t>0.2003</t>
+          <t>0.133</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr">
         <is>
-          <t>0.3485</t>
+          <t>0.3077</t>
         </is>
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>72.09</t>
+          <t>71.52</t>
         </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
-          <t>22.74</t>
+          <t>19.28</t>
         </is>
       </c>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>43.85</t>
+          <t>35.31</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>29.88</t>
+          <t>25.06</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>15.6</t>
+          <t>15.7</t>
         </is>
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>0.1906</t>
+          <t>0.1523</t>
         </is>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>10.46</t>
         </is>
       </c>
       <c r="BB36" t="inlineStr">
         <is>
-          <t>37.6</t>
+          <t>42.78</t>
         </is>
       </c>
       <c r="BC36" t="inlineStr">
         <is>
-          <t>87.9</t>
+          <t>89.79</t>
         </is>
       </c>
       <c r="BD36" t="inlineStr">
         <is>
-          <t>0.411</t>
+          <t>0.5078</t>
         </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.2263</t>
         </is>
       </c>
       <c r="BF36" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="BG36" t="inlineStr"/>
       <c r="BH36" t="inlineStr"/>
       <c r="BI36" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>Citizens Bank Park</t>
         </is>
       </c>
       <c r="BJ36" t="inlineStr"/>
@@ -10395,27 +10395,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>607208</t>
+          <t>687749</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Trea Turner</t>
+          <t>Jase Bowen</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-08-06T22:05:00Z</t>
+          <t>2026-08-07T01:40:00Z</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -10425,22 +10425,22 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Miles Mikolas</t>
+          <t>Kohl Drake</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>571945</t>
+          <t>684442</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L37" t="n">
@@ -10458,26 +10458,26 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Strong Barrel, Pitcher Vulnerable, Platoon Edge</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>28.9</v>
+        <v>37</v>
       </c>
       <c r="Q37" t="n">
-        <v>61.4</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="R37" t="n">
-        <v>34.3</v>
+        <v>28.2</v>
       </c>
       <c r="S37" t="n">
-        <v>95.5</v>
+        <v>40.2</v>
       </c>
       <c r="T37" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U37" t="n">
-        <v>75.59999999999999</v>
+        <v>26.8</v>
       </c>
       <c r="V37" t="inlineStr">
         <is>
@@ -10491,7 +10491,7 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
@@ -10516,7 +10516,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026</t>
         </is>
       </c>
       <c r="AD37" t="inlineStr"/>
@@ -10533,134 +10533,134 @@
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 3/17, 1 HR</t>
         </is>
       </c>
       <c r="AL37" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.5% barrel, 26.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 15.0% barrel, 3.0 HR allowed</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>6.36</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>41.54</t>
+          <t>35.7</t>
         </is>
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>88.95</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="AQ37" t="inlineStr">
         <is>
-          <t>99.574</t>
+          <t>99.7068</t>
         </is>
       </c>
       <c r="AR37" t="inlineStr">
         <is>
-          <t>0.3918</t>
+          <t>0.368</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>0.148</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr">
         <is>
-          <t>0.3077</t>
+          <t>0.276</t>
         </is>
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>71.52</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
-          <t>19.28</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>35.31</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>25.06</t>
+          <t>33.3</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
-          <t>15.7</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>0.1523</t>
+          <t>0.073</t>
         </is>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
-          <t>10.46</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="BB37" t="inlineStr">
         <is>
-          <t>42.78</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="BC37" t="inlineStr">
         <is>
-          <t>89.79</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="BD37" t="inlineStr">
         <is>
-          <t>0.5078</t>
+          <t>0.594</t>
         </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
-          <t>0.2263</t>
+          <t>0.295</t>
         </is>
       </c>
       <c r="BF37" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="BG37" t="inlineStr"/>
       <c r="BH37" t="inlineStr"/>
       <c r="BI37" t="inlineStr">
         <is>
-          <t>Citizens Bank Park</t>
+          <t>Chase Field</t>
         </is>
       </c>
       <c r="BJ37" t="inlineStr"/>
@@ -10720,7 +10720,7 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>50.8</v>
+        <v>50.7</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
@@ -10753,7 +10753,7 @@
         <v>80</v>
       </c>
       <c r="U38" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="V38" t="inlineStr">
         <is>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ38" t="inlineStr">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 0 HR</t>
+          <t>Last 7 games: 6/25, 0 HR</t>
         </is>
       </c>
       <c r="AL38" t="inlineStr">
@@ -11581,7 +11581,7 @@
         <v>50</v>
       </c>
       <c r="U41" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V41" t="inlineStr">
         <is>
@@ -11642,7 +11642,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ41" t="inlineStr">
@@ -11652,7 +11652,7 @@
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 0 HR</t>
+          <t>Last 7 games: 4/25, 0 HR</t>
         </is>
       </c>
       <c r="AL41" t="inlineStr">
@@ -12879,27 +12879,27 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>668804</t>
+          <t>693307</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bryan Reynolds</t>
+          <t>Dillon Dingler</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-08-06T18:10:00Z</t>
+          <t>2026-08-06T20:10:00Z</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -12914,12 +12914,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Dustin May</t>
+          <t>Bryce Miller</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>669160</t>
+          <t>682243</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -12928,7 +12928,7 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>49.5</v>
+        <v>49.6</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
@@ -12942,26 +12942,26 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P46" t="n">
-        <v>46.1</v>
+        <v>47.4</v>
       </c>
       <c r="Q46" t="n">
-        <v>40</v>
+        <v>36.5</v>
       </c>
       <c r="R46" t="n">
-        <v>27.6</v>
+        <v>25.4</v>
       </c>
       <c r="S46" t="n">
         <v>92.09999999999999</v>
       </c>
       <c r="T46" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U46" t="n">
-        <v>18.2</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="V46" t="inlineStr">
         <is>
@@ -13017,134 +13017,134 @@
       </c>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>35</t>
         </is>
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/29, 0 HR</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL46" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 7.3% barrel, 11.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.2% barrel, 13.5 HR allowed</t>
         </is>
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN46" t="inlineStr">
         <is>
-          <t>10.87</t>
+          <t>10.67</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>46.28</t>
+          <t>45.14</t>
         </is>
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>90.92</t>
+          <t>89.44</t>
         </is>
       </c>
       <c r="AQ46" t="inlineStr">
         <is>
-          <t>101.878</t>
+          <t>100.9658</t>
         </is>
       </c>
       <c r="AR46" t="inlineStr">
         <is>
-          <t>0.4386</t>
+          <t>0.5009</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr">
         <is>
-          <t>0.1876</t>
+          <t>0.2144</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr">
         <is>
-          <t>0.3478</t>
+          <t>0.3664</t>
         </is>
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>72.62</t>
+          <t>71.77</t>
         </is>
       </c>
       <c r="AV46" t="inlineStr">
         <is>
-          <t>28.37</t>
+          <t>15.62</t>
         </is>
       </c>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>40.22</t>
+          <t>40.45</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>25.46</t>
+          <t>28.36</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
-          <t>15.3</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>0.171</t>
+          <t>0.2177</t>
         </is>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
-          <t>7.31</t>
+          <t>7.16</t>
         </is>
       </c>
       <c r="BB46" t="inlineStr">
         <is>
-          <t>45.62</t>
+          <t>36.7</t>
         </is>
       </c>
       <c r="BC46" t="inlineStr">
         <is>
-          <t>90.25</t>
+          <t>88.83</t>
         </is>
       </c>
       <c r="BD46" t="inlineStr">
         <is>
-          <t>0.395</t>
+          <t>0.3769</t>
         </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
-          <t>0.1455</t>
+          <t>0.1512</t>
         </is>
       </c>
       <c r="BF46" t="inlineStr">
         <is>
-          <t>24.31</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="BG46" t="inlineStr"/>
       <c r="BH46" t="inlineStr"/>
       <c r="BI46" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>T-Mobile Park</t>
         </is>
       </c>
       <c r="BJ46" t="inlineStr"/>
@@ -13155,27 +13155,27 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>669134</t>
+          <t>668804</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Luis Campusano</t>
+          <t>Bryan Reynolds</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-08-07T01:40:00Z</t>
+          <t>2026-08-06T18:10:00Z</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -13185,26 +13185,26 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Kohl Drake</t>
+          <t>Dustin May</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>684442</t>
+          <t>669160</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>49.4</v>
+        <v>49.5</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
@@ -13218,26 +13218,26 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Projected Lineup, Pitcher Vulnerable, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P47" t="n">
-        <v>20.7</v>
+        <v>46.1</v>
       </c>
       <c r="Q47" t="n">
-        <v>86.09999999999999</v>
+        <v>40</v>
       </c>
       <c r="R47" t="n">
-        <v>28.2</v>
+        <v>27.6</v>
       </c>
       <c r="S47" t="n">
-        <v>59.8</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T47" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="U47" t="n">
-        <v>45</v>
+        <v>18.2</v>
       </c>
       <c r="V47" t="inlineStr">
         <is>
@@ -13251,7 +13251,7 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
@@ -13276,7 +13276,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD47" t="inlineStr"/>
@@ -13293,12 +13293,12 @@
       </c>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ47" t="inlineStr">
@@ -13308,119 +13308,119 @@
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>Contact streak: 10/23 over last 7 games</t>
+          <t>Last 7 games: 7/29, 0 HR</t>
         </is>
       </c>
       <c r="AL47" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 15.0% barrel, 3.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 7.3% barrel, 11.2 HR allowed</t>
         </is>
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN47" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>10.87</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>39.94</t>
+          <t>46.28</t>
         </is>
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>87.87</t>
+          <t>90.92</t>
         </is>
       </c>
       <c r="AQ47" t="inlineStr">
         <is>
-          <t>99.166</t>
+          <t>101.878</t>
         </is>
       </c>
       <c r="AR47" t="inlineStr">
         <is>
-          <t>0.3102</t>
+          <t>0.4386</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr">
         <is>
-          <t>0.105</t>
+          <t>0.1876</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr">
         <is>
-          <t>0.3025</t>
+          <t>0.3478</t>
         </is>
       </c>
       <c r="AU47" t="inlineStr">
         <is>
-          <t>72.54</t>
+          <t>72.62</t>
         </is>
       </c>
       <c r="AV47" t="inlineStr">
         <is>
-          <t>25.72</t>
+          <t>28.37</t>
         </is>
       </c>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>48.03</t>
+          <t>40.22</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>18.47</t>
+          <t>25.46</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>15.3</t>
         </is>
       </c>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.171</t>
         </is>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>7.31</t>
         </is>
       </c>
       <c r="BB47" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>45.62</t>
         </is>
       </c>
       <c r="BC47" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>90.25</t>
         </is>
       </c>
       <c r="BD47" t="inlineStr">
         <is>
-          <t>0.594</t>
+          <t>0.395</t>
         </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
-          <t>0.295</t>
+          <t>0.1455</t>
         </is>
       </c>
       <c r="BF47" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>24.31</t>
         </is>
       </c>
       <c r="BG47" t="inlineStr"/>
       <c r="BH47" t="inlineStr"/>
       <c r="BI47" t="inlineStr">
         <is>
-          <t>Chase Field</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ47" t="inlineStr"/>
@@ -13431,27 +13431,27 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>680776</t>
+          <t>677594</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Jarren Duran</t>
+          <t>Julio Rodriguez</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-08-06T23:10:00Z</t>
+          <t>2026-08-06T20:10:00Z</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -13461,26 +13461,26 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Luis Castillo</t>
+          <t>Framber Valdez</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>622491</t>
+          <t>664285</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>48.9</v>
+        <v>49.3</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
@@ -13494,26 +13494,26 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P48" t="n">
-        <v>38.6</v>
+        <v>45.7</v>
       </c>
       <c r="Q48" t="n">
-        <v>54</v>
+        <v>36.2</v>
       </c>
       <c r="R48" t="n">
-        <v>28.7</v>
+        <v>25.4</v>
       </c>
       <c r="S48" t="n">
-        <v>59.8</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T48" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U48" t="n">
-        <v>66.7</v>
+        <v>40.7</v>
       </c>
       <c r="V48" t="inlineStr">
         <is>
@@ -13527,7 +13527,7 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
@@ -13569,27 +13569,27 @@
       </c>
       <c r="AH48" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 7/26, 1 HR</t>
         </is>
       </c>
       <c r="AL48" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.9% barrel, 18.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.4% barrel, 12.9 HR allowed</t>
         </is>
       </c>
       <c r="AM48" t="inlineStr">
@@ -13599,104 +13599,104 @@
       </c>
       <c r="AN48" t="inlineStr">
         <is>
-          <t>10.05</t>
+          <t>8.89</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>40.71</t>
+          <t>44.22</t>
         </is>
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>90.12</t>
+          <t>90.47</t>
         </is>
       </c>
       <c r="AQ48" t="inlineStr">
         <is>
-          <t>101.8422</t>
+          <t>102.7276</t>
         </is>
       </c>
       <c r="AR48" t="inlineStr">
         <is>
-          <t>0.3932</t>
+          <t>0.4692</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr">
         <is>
-          <t>0.155</t>
+          <t>0.1957</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr">
         <is>
-          <t>0.3071</t>
+          <t>0.3468</t>
         </is>
       </c>
       <c r="AU48" t="inlineStr">
         <is>
-          <t>74.98</t>
+          <t>76.61</t>
         </is>
       </c>
       <c r="AV48" t="inlineStr">
         <is>
-          <t>50.03</t>
+          <t>66.64</t>
         </is>
       </c>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>38.76</t>
+          <t>37.93</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>22.44</t>
+          <t>26.05</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
-          <t>15.3</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>0.1615</t>
+          <t>0.1727</t>
         </is>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
-          <t>9.91</t>
+          <t>6.42</t>
         </is>
       </c>
       <c r="BB48" t="inlineStr">
         <is>
-          <t>43.11</t>
+          <t>44.27</t>
         </is>
       </c>
       <c r="BC48" t="inlineStr">
         <is>
-          <t>90.23</t>
+          <t>90.17</t>
         </is>
       </c>
       <c r="BD48" t="inlineStr">
         <is>
-          <t>0.4418</t>
+          <t>0.3847</t>
         </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
-          <t>0.1814</t>
+          <t>0.1353</t>
         </is>
       </c>
       <c r="BF48" t="inlineStr">
         <is>
-          <t>27.93</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="BG48" t="inlineStr"/>
       <c r="BH48" t="inlineStr"/>
       <c r="BI48" t="inlineStr">
         <is>
-          <t>Fenway Park</t>
+          <t>T-Mobile Park</t>
         </is>
       </c>
       <c r="BJ48" t="inlineStr"/>
@@ -13707,27 +13707,27 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>678246</t>
+          <t>669134</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Miguel Vargas</t>
+          <t>Luis Campusano</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-08-06T23:10:00Z</t>
+          <t>2026-08-07T01:40:00Z</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Ranger Suarez</t>
+          <t>Kohl Drake</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>624133</t>
+          <t>684442</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -13756,7 +13756,7 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>48.8</v>
+        <v>49.1</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
@@ -13770,26 +13770,26 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Pitcher Vulnerable, Platoon Edge</t>
         </is>
       </c>
       <c r="P49" t="n">
-        <v>55.3</v>
+        <v>20.7</v>
       </c>
       <c r="Q49" t="n">
-        <v>16.6</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="R49" t="n">
-        <v>28.7</v>
+        <v>28.2</v>
       </c>
       <c r="S49" t="n">
-        <v>92.09999999999999</v>
+        <v>59.8</v>
       </c>
       <c r="T49" t="n">
         <v>78</v>
       </c>
       <c r="U49" t="n">
-        <v>47.5</v>
+        <v>39.7</v>
       </c>
       <c r="V49" t="inlineStr">
         <is>
@@ -13803,7 +13803,7 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
@@ -13828,7 +13828,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD49" t="inlineStr"/>
@@ -13845,7 +13845,7 @@
       </c>
       <c r="AH49" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI49" t="inlineStr">
@@ -13855,124 +13855,124 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 10/26 over last 7 games</t>
         </is>
       </c>
       <c r="AL49" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.9% barrel, 7.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 15.0% barrel, 3.0 HR allowed</t>
         </is>
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN49" t="inlineStr">
         <is>
-          <t>13.04</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>44.91</t>
+          <t>39.94</t>
         </is>
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>90.47</t>
+          <t>87.87</t>
         </is>
       </c>
       <c r="AQ49" t="inlineStr">
         <is>
-          <t>100.6121</t>
+          <t>99.166</t>
         </is>
       </c>
       <c r="AR49" t="inlineStr">
         <is>
-          <t>0.4896</t>
+          <t>0.3102</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr">
         <is>
-          <t>0.2312</t>
+          <t>0.105</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr">
         <is>
-          <t>0.3673</t>
+          <t>0.3025</t>
         </is>
       </c>
       <c r="AU49" t="inlineStr">
         <is>
-          <t>73.05</t>
+          <t>72.54</t>
         </is>
       </c>
       <c r="AV49" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>25.72</t>
         </is>
       </c>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>48.03</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>36.22</t>
+          <t>18.47</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>0.2188</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="BB49" t="inlineStr">
         <is>
-          <t>32.57</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="BC49" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="BD49" t="inlineStr">
         <is>
-          <t>0.3447</t>
+          <t>0.594</t>
         </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
-          <t>0.1068</t>
+          <t>0.295</t>
         </is>
       </c>
       <c r="BF49" t="inlineStr">
         <is>
-          <t>22.49</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="BG49" t="inlineStr"/>
       <c r="BH49" t="inlineStr"/>
       <c r="BI49" t="inlineStr">
         <is>
-          <t>Fenway Park</t>
+          <t>Chase Field</t>
         </is>
       </c>
       <c r="BJ49" t="inlineStr"/>
@@ -13983,27 +13983,27 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>543807</t>
+          <t>680776</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>George Springer</t>
+          <t>Jarren Duran</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-08-06T18:20:00Z</t>
+          <t>2026-08-06T23:10:00Z</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -14013,26 +14013,26 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>David Peterson</t>
+          <t>Luis Castillo</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>656849</t>
+          <t>622491</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>48.7</v>
+        <v>48.9</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
@@ -14046,26 +14046,26 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P50" t="n">
-        <v>42.3</v>
+        <v>38.6</v>
       </c>
       <c r="Q50" t="n">
-        <v>39.1</v>
+        <v>54</v>
       </c>
       <c r="R50" t="n">
-        <v>29.8</v>
+        <v>28.7</v>
       </c>
       <c r="S50" t="n">
-        <v>90.40000000000001</v>
+        <v>59.8</v>
       </c>
       <c r="T50" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U50" t="n">
-        <v>24</v>
+        <v>66.7</v>
       </c>
       <c r="V50" t="inlineStr">
         <is>
@@ -14079,7 +14079,7 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
@@ -14121,7 +14121,7 @@
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI50" t="inlineStr">
@@ -14131,17 +14131,17 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/25, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL50" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 11.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.9% barrel, 18.1 HR allowed</t>
         </is>
       </c>
       <c r="AM50" t="inlineStr">
@@ -14151,104 +14151,104 @@
       </c>
       <c r="AN50" t="inlineStr">
         <is>
-          <t>10.11</t>
+          <t>10.05</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>42.42</t>
+          <t>40.71</t>
         </is>
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>89.23</t>
+          <t>90.12</t>
         </is>
       </c>
       <c r="AQ50" t="inlineStr">
         <is>
-          <t>100.442</t>
+          <t>101.8422</t>
         </is>
       </c>
       <c r="AR50" t="inlineStr">
         <is>
-          <t>0.4415</t>
+          <t>0.3932</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr">
         <is>
-          <t>0.1904</t>
+          <t>0.155</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr">
         <is>
-          <t>0.3389</t>
+          <t>0.3071</t>
         </is>
       </c>
       <c r="AU50" t="inlineStr">
         <is>
-          <t>73.24</t>
+          <t>74.98</t>
         </is>
       </c>
       <c r="AV50" t="inlineStr">
         <is>
-          <t>35.02</t>
+          <t>50.03</t>
         </is>
       </c>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>41.72</t>
+          <t>38.76</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>27.56</t>
+          <t>22.44</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>15.3</t>
         </is>
       </c>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>0.1929</t>
+          <t>0.1615</t>
         </is>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
-          <t>6.89</t>
+          <t>9.91</t>
         </is>
       </c>
       <c r="BB50" t="inlineStr">
         <is>
-          <t>43.55</t>
+          <t>43.11</t>
         </is>
       </c>
       <c r="BC50" t="inlineStr">
         <is>
-          <t>90.11</t>
+          <t>90.23</t>
         </is>
       </c>
       <c r="BD50" t="inlineStr">
         <is>
-          <t>0.4217</t>
+          <t>0.4418</t>
         </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
-          <t>0.1482</t>
+          <t>0.1814</t>
         </is>
       </c>
       <c r="BF50" t="inlineStr">
         <is>
-          <t>19.85</t>
+          <t>27.93</t>
         </is>
       </c>
       <c r="BG50" t="inlineStr"/>
       <c r="BH50" t="inlineStr"/>
       <c r="BI50" t="inlineStr">
         <is>
-          <t>Wrigley Field</t>
+          <t>Fenway Park</t>
         </is>
       </c>
       <c r="BJ50" t="inlineStr"/>
@@ -14259,27 +14259,27 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>693307</t>
+          <t>678246</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Dillon Dingler</t>
+          <t>Miguel Vargas</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-06T20:10:00Z</t>
+          <t>2026-08-06T23:10:00Z</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -14294,21 +14294,21 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Bryce Miller</t>
+          <t>Ranger Suarez</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>682243</t>
+          <t>624133</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>48.5</v>
+        <v>48.8</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
@@ -14322,26 +14322,26 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P51" t="n">
-        <v>47.4</v>
+        <v>55.3</v>
       </c>
       <c r="Q51" t="n">
-        <v>36.5</v>
+        <v>16.6</v>
       </c>
       <c r="R51" t="n">
-        <v>25.4</v>
+        <v>28.7</v>
       </c>
       <c r="S51" t="n">
         <v>92.09999999999999</v>
       </c>
       <c r="T51" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U51" t="n">
-        <v>58.4</v>
+        <v>47.5</v>
       </c>
       <c r="V51" t="inlineStr">
         <is>
@@ -14397,12 +14397,12 @@
       </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ51" t="inlineStr">
@@ -14417,114 +14417,114 @@
       </c>
       <c r="AL51" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.2% barrel, 13.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.9% barrel, 7.7 HR allowed</t>
         </is>
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN51" t="inlineStr">
         <is>
-          <t>10.67</t>
+          <t>13.04</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>45.14</t>
+          <t>44.91</t>
         </is>
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>89.44</t>
+          <t>90.47</t>
         </is>
       </c>
       <c r="AQ51" t="inlineStr">
         <is>
-          <t>100.9658</t>
+          <t>100.6121</t>
         </is>
       </c>
       <c r="AR51" t="inlineStr">
         <is>
-          <t>0.5009</t>
+          <t>0.4896</t>
         </is>
       </c>
       <c r="AS51" t="inlineStr">
         <is>
-          <t>0.2144</t>
+          <t>0.2312</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr">
         <is>
-          <t>0.3664</t>
+          <t>0.3673</t>
         </is>
       </c>
       <c r="AU51" t="inlineStr">
         <is>
-          <t>71.77</t>
+          <t>73.05</t>
         </is>
       </c>
       <c r="AV51" t="inlineStr">
         <is>
-          <t>15.62</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>40.45</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>28.36</t>
+          <t>36.22</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>0.2177</t>
+          <t>0.2188</t>
         </is>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
-          <t>7.16</t>
+          <t>4.94</t>
         </is>
       </c>
       <c r="BB51" t="inlineStr">
         <is>
-          <t>36.7</t>
+          <t>32.57</t>
         </is>
       </c>
       <c r="BC51" t="inlineStr">
         <is>
-          <t>88.83</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="BD51" t="inlineStr">
         <is>
-          <t>0.3769</t>
+          <t>0.3447</t>
         </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
-          <t>0.1512</t>
+          <t>0.1068</t>
         </is>
       </c>
       <c r="BF51" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>22.49</t>
         </is>
       </c>
       <c r="BG51" t="inlineStr"/>
       <c r="BH51" t="inlineStr"/>
       <c r="BI51" t="inlineStr">
         <is>
-          <t>T-Mobile Park</t>
+          <t>Fenway Park</t>
         </is>
       </c>
       <c r="BJ51" t="inlineStr"/>
@@ -14535,27 +14535,27 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>605137</t>
+          <t>543807</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Josh Bell</t>
+          <t>George Springer</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-08-06T23:40:00Z</t>
+          <t>2026-08-06T18:20:00Z</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -14565,26 +14565,26 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Michael Wacha</t>
+          <t>David Peterson</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>608379</t>
+          <t>656849</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>48.5</v>
+        <v>48.7</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
@@ -14602,22 +14602,22 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>45.7</v>
+        <v>42.3</v>
       </c>
       <c r="Q52" t="n">
-        <v>34.5</v>
+        <v>39.1</v>
       </c>
       <c r="R52" t="n">
-        <v>23.2</v>
+        <v>29.8</v>
       </c>
       <c r="S52" t="n">
-        <v>92.09999999999999</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T52" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="U52" t="n">
-        <v>40.7</v>
+        <v>24</v>
       </c>
       <c r="V52" t="inlineStr">
         <is>
@@ -14631,7 +14631,7 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
@@ -14678,22 +14678,22 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/26, 1 HR</t>
+          <t>Last 7 games: 7/25, 0 HR</t>
         </is>
       </c>
       <c r="AL52" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.7% barrel, 15.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 11.0 HR allowed</t>
         </is>
       </c>
       <c r="AM52" t="inlineStr">
@@ -14703,104 +14703,104 @@
       </c>
       <c r="AN52" t="inlineStr">
         <is>
-          <t>10.7</t>
+          <t>10.11</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>44.27</t>
+          <t>42.42</t>
         </is>
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>90.19</t>
+          <t>89.23</t>
         </is>
       </c>
       <c r="AQ52" t="inlineStr">
         <is>
-          <t>101.0642</t>
+          <t>100.442</t>
         </is>
       </c>
       <c r="AR52" t="inlineStr">
         <is>
-          <t>0.4514</t>
+          <t>0.4415</t>
         </is>
       </c>
       <c r="AS52" t="inlineStr">
         <is>
-          <t>0.2024</t>
+          <t>0.1904</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr">
         <is>
-          <t>0.3331</t>
+          <t>0.3389</t>
         </is>
       </c>
       <c r="AU52" t="inlineStr">
         <is>
-          <t>72.33</t>
+          <t>73.24</t>
         </is>
       </c>
       <c r="AV52" t="inlineStr">
         <is>
-          <t>28.29</t>
+          <t>35.02</t>
         </is>
       </c>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>41.29</t>
+          <t>41.72</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>26.92</t>
+          <t>27.56</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
-          <t>16.4</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>0.1723</t>
+          <t>0.1929</t>
         </is>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
-          <t>6.7</t>
+          <t>6.89</t>
         </is>
       </c>
       <c r="BB52" t="inlineStr">
         <is>
-          <t>36.42</t>
+          <t>43.55</t>
         </is>
       </c>
       <c r="BC52" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>90.11</t>
         </is>
       </c>
       <c r="BD52" t="inlineStr">
         <is>
-          <t>0.4144</t>
+          <t>0.4217</t>
         </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
-          <t>0.1612</t>
+          <t>0.1482</t>
         </is>
       </c>
       <c r="BF52" t="inlineStr">
         <is>
-          <t>27.83</t>
+          <t>19.85</t>
         </is>
       </c>
       <c r="BG52" t="inlineStr"/>
       <c r="BH52" t="inlineStr"/>
       <c r="BI52" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>Wrigley Field</t>
         </is>
       </c>
       <c r="BJ52" t="inlineStr"/>
@@ -14860,7 +14860,7 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>48.3</v>
+        <v>48.7</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
@@ -14893,7 +14893,7 @@
         <v>78</v>
       </c>
       <c r="U53" t="n">
-        <v>42.3</v>
+        <v>50.3</v>
       </c>
       <c r="V53" t="inlineStr">
         <is>
@@ -14949,12 +14949,12 @@
       </c>
       <c r="AH53" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ53" t="inlineStr">
@@ -14964,7 +14964,7 @@
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/25, 1 HR</t>
+          <t>Contact streak: 9/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL53" t="inlineStr">
@@ -15087,27 +15087,27 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>691016</t>
+          <t>605137</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Tyler Soderstrom</t>
+          <t>Josh Bell</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-08-06T16:40:00Z</t>
+          <t>2026-08-06T23:40:00Z</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -15122,21 +15122,21 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Andrew Abbott</t>
+          <t>Michael Wacha</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>671096</t>
+          <t>608379</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>48.2</v>
+        <v>48.5</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
@@ -15150,26 +15150,26 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P54" t="n">
-        <v>44.8</v>
+        <v>45.7</v>
       </c>
       <c r="Q54" t="n">
-        <v>40.2</v>
+        <v>34.5</v>
       </c>
       <c r="R54" t="n">
-        <v>39.3</v>
+        <v>23.2</v>
       </c>
       <c r="S54" t="n">
         <v>92.09999999999999</v>
       </c>
       <c r="T54" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U54" t="n">
-        <v>9.800000000000001</v>
+        <v>40.7</v>
       </c>
       <c r="V54" t="inlineStr">
         <is>
@@ -15225,27 +15225,27 @@
       </c>
       <c r="AH54" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/27, 0 HR</t>
+          <t>Last 7 games: 7/26, 1 HR</t>
         </is>
       </c>
       <c r="AL54" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.7% barrel, 17.6 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.7% barrel, 15.7 HR allowed</t>
         </is>
       </c>
       <c r="AM54" t="inlineStr">
@@ -15255,104 +15255,104 @@
       </c>
       <c r="AN54" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>10.7</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>47.14</t>
+          <t>44.27</t>
         </is>
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>90.83</t>
+          <t>90.19</t>
         </is>
       </c>
       <c r="AQ54" t="inlineStr">
         <is>
-          <t>102.087</t>
+          <t>101.0642</t>
         </is>
       </c>
       <c r="AR54" t="inlineStr">
         <is>
-          <t>0.4283</t>
+          <t>0.4514</t>
         </is>
       </c>
       <c r="AS54" t="inlineStr">
         <is>
-          <t>0.1736</t>
+          <t>0.2024</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr">
         <is>
-          <t>0.3354</t>
+          <t>0.3331</t>
         </is>
       </c>
       <c r="AU54" t="inlineStr">
         <is>
-          <t>74.25</t>
+          <t>72.33</t>
         </is>
       </c>
       <c r="AV54" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>28.29</t>
         </is>
       </c>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>36.56</t>
+          <t>41.29</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>25.81</t>
+          <t>26.92</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>16.4</t>
         </is>
       </c>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>0.2127</t>
+          <t>0.1723</t>
         </is>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
-          <t>7.65</t>
+          <t>6.7</t>
         </is>
       </c>
       <c r="BB54" t="inlineStr">
         <is>
-          <t>36.71</t>
+          <t>36.42</t>
         </is>
       </c>
       <c r="BC54" t="inlineStr">
         <is>
-          <t>89.06</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="BD54" t="inlineStr">
         <is>
-          <t>0.4081</t>
+          <t>0.4144</t>
         </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
-          <t>0.1597</t>
+          <t>0.1612</t>
         </is>
       </c>
       <c r="BF54" t="inlineStr">
         <is>
-          <t>28.28</t>
+          <t>27.83</t>
         </is>
       </c>
       <c r="BG54" t="inlineStr"/>
       <c r="BH54" t="inlineStr"/>
       <c r="BI54" t="inlineStr">
         <is>
-          <t>Great American Ball Park</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ54" t="inlineStr"/>
@@ -15363,27 +15363,27 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>677594</t>
+          <t>691016</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Julio Rodriguez</t>
+          <t>Tyler Soderstrom</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-08-06T20:10:00Z</t>
+          <t>2026-08-06T16:40:00Z</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -15393,17 +15393,17 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Framber Valdez</t>
+          <t>Andrew Abbott</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>664285</t>
+          <t>671096</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -15426,26 +15426,26 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P55" t="n">
-        <v>45.7</v>
+        <v>44.8</v>
       </c>
       <c r="Q55" t="n">
-        <v>36.2</v>
+        <v>40.2</v>
       </c>
       <c r="R55" t="n">
-        <v>25.4</v>
+        <v>39.3</v>
       </c>
       <c r="S55" t="n">
-        <v>90.40000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T55" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U55" t="n">
-        <v>19.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="V55" t="inlineStr">
         <is>
@@ -15459,7 +15459,7 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr">
@@ -15501,12 +15501,12 @@
       </c>
       <c r="AH55" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ55" t="inlineStr">
@@ -15516,12 +15516,12 @@
       </c>
       <c r="AK55" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 0 HR</t>
+          <t>Last 7 games: 5/27, 0 HR</t>
         </is>
       </c>
       <c r="AL55" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.4% barrel, 12.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.7% barrel, 17.6 HR allowed</t>
         </is>
       </c>
       <c r="AM55" t="inlineStr">
@@ -15531,104 +15531,104 @@
       </c>
       <c r="AN55" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>44.22</t>
+          <t>47.14</t>
         </is>
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>90.47</t>
+          <t>90.83</t>
         </is>
       </c>
       <c r="AQ55" t="inlineStr">
         <is>
-          <t>102.7276</t>
+          <t>102.087</t>
         </is>
       </c>
       <c r="AR55" t="inlineStr">
         <is>
-          <t>0.4692</t>
+          <t>0.4283</t>
         </is>
       </c>
       <c r="AS55" t="inlineStr">
         <is>
-          <t>0.1957</t>
+          <t>0.1736</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr">
         <is>
-          <t>0.3468</t>
+          <t>0.3354</t>
         </is>
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>76.61</t>
+          <t>74.25</t>
         </is>
       </c>
       <c r="AV55" t="inlineStr">
         <is>
-          <t>66.64</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>37.93</t>
+          <t>36.56</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>26.05</t>
+          <t>25.81</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>0.1727</t>
+          <t>0.2127</t>
         </is>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
-          <t>6.42</t>
+          <t>7.65</t>
         </is>
       </c>
       <c r="BB55" t="inlineStr">
         <is>
-          <t>44.27</t>
+          <t>36.71</t>
         </is>
       </c>
       <c r="BC55" t="inlineStr">
         <is>
-          <t>90.17</t>
+          <t>89.06</t>
         </is>
       </c>
       <c r="BD55" t="inlineStr">
         <is>
-          <t>0.3847</t>
+          <t>0.4081</t>
         </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
-          <t>0.1353</t>
+          <t>0.1597</t>
         </is>
       </c>
       <c r="BF55" t="inlineStr">
         <is>
-          <t>19.3</t>
+          <t>28.28</t>
         </is>
       </c>
       <c r="BG55" t="inlineStr"/>
       <c r="BH55" t="inlineStr"/>
       <c r="BI55" t="inlineStr">
         <is>
-          <t>T-Mobile Park</t>
+          <t>Great American Ball Park</t>
         </is>
       </c>
       <c r="BJ55" t="inlineStr"/>
@@ -17653,7 +17653,7 @@
         <v>75</v>
       </c>
       <c r="U63" t="n">
-        <v>19.1</v>
+        <v>18.3</v>
       </c>
       <c r="V63" t="inlineStr">
         <is>
@@ -17714,7 +17714,7 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ63" t="inlineStr">
@@ -17724,7 +17724,7 @@
       </c>
       <c r="AK63" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/24, 1 HR</t>
+          <t>Last 7 games: 3/25, 1 HR</t>
         </is>
       </c>
       <c r="AL63" t="inlineStr">
@@ -20055,27 +20055,27 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>679529</t>
+          <t>701807</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spencer Torkelson</t>
+          <t>Carson Benge</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-08-06T20:10:00Z</t>
+          <t>2026-08-06T17:10:00Z</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -20085,26 +20085,26 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Bryce Miller</t>
+          <t>Foster Griffin</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>682243</t>
+          <t>656492</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>46.1</v>
+        <v>46</v>
       </c>
       <c r="M72" t="inlineStr">
         <is>
@@ -20118,26 +20118,26 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P72" t="n">
-        <v>49.8</v>
+        <v>34.1</v>
       </c>
       <c r="Q72" t="n">
-        <v>36.5</v>
+        <v>42.2</v>
       </c>
       <c r="R72" t="n">
-        <v>25.4</v>
+        <v>27.6</v>
       </c>
       <c r="S72" t="n">
-        <v>71.7</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T72" t="n">
         <v>50</v>
       </c>
       <c r="U72" t="n">
-        <v>50.3</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="V72" t="inlineStr">
         <is>
@@ -20151,7 +20151,7 @@
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y72" t="inlineStr">
@@ -20176,7 +20176,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026</t>
         </is>
       </c>
       <c r="AD72" t="inlineStr"/>
@@ -20193,134 +20193,134 @@
       </c>
       <c r="AH72" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI72" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
         <is>
-          <t>Contact streak: 10/30 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL72" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.2% barrel, 13.5 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.2% barrel, 19.0 HR allowed</t>
         </is>
       </c>
       <c r="AM72" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN72" t="inlineStr">
         <is>
-          <t>13.22</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>42.58</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>89.78</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AQ72" t="inlineStr">
         <is>
-          <t>100.3127</t>
+          <t>100.0599</t>
         </is>
       </c>
       <c r="AR72" t="inlineStr">
         <is>
-          <t>0.4238</t>
+          <t>0.434</t>
         </is>
       </c>
       <c r="AS72" t="inlineStr">
         <is>
-          <t>0.2027</t>
+          <t>0.157</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr">
         <is>
-          <t>0.3207</t>
+          <t>0.338</t>
         </is>
       </c>
       <c r="AU72" t="inlineStr">
         <is>
-          <t>73.14</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AV72" t="inlineStr">
         <is>
-          <t>26.09</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>47.98</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>36.74</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
-          <t>23.3</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>0.2083</t>
+          <t>0.135</t>
         </is>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
-          <t>7.16</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="BB72" t="inlineStr">
         <is>
-          <t>36.7</t>
+          <t>37.6</t>
         </is>
       </c>
       <c r="BC72" t="inlineStr">
         <is>
-          <t>88.83</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="BD72" t="inlineStr">
         <is>
-          <t>0.3769</t>
+          <t>0.411</t>
         </is>
       </c>
       <c r="BE72" t="inlineStr">
         <is>
-          <t>0.1512</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="BF72" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="BG72" t="inlineStr"/>
       <c r="BH72" t="inlineStr"/>
       <c r="BI72" t="inlineStr">
         <is>
-          <t>T-Mobile Park</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BJ72" t="inlineStr"/>
@@ -20331,27 +20331,27 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>701807</t>
+          <t>805808</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Carson Benge</t>
+          <t>Kevin McGonigle</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-08-06T17:10:00Z</t>
+          <t>2026-08-06T20:10:00Z</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -20361,26 +20361,26 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Foster Griffin</t>
+          <t>Bryce Miller</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>656492</t>
+          <t>682243</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>46</v>
+        <v>45.9</v>
       </c>
       <c r="M73" t="inlineStr">
         <is>
@@ -20394,26 +20394,26 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P73" t="n">
-        <v>34.1</v>
+        <v>32.4</v>
       </c>
       <c r="Q73" t="n">
-        <v>42.2</v>
+        <v>36.5</v>
       </c>
       <c r="R73" t="n">
-        <v>27.6</v>
+        <v>25.4</v>
       </c>
       <c r="S73" t="n">
-        <v>90.40000000000001</v>
+        <v>88.7</v>
       </c>
       <c r="T73" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U73" t="n">
-        <v>66.90000000000001</v>
+        <v>60</v>
       </c>
       <c r="V73" t="inlineStr">
         <is>
@@ -20427,7 +20427,7 @@
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y73" t="inlineStr">
@@ -20452,7 +20452,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>H:2026 P:2026</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD73" t="inlineStr"/>
@@ -20469,12 +20469,12 @@
       </c>
       <c r="AH73" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ73" t="inlineStr">
@@ -20489,114 +20489,114 @@
       </c>
       <c r="AL73" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.2% barrel, 19.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.2% barrel, 13.5 HR allowed</t>
         </is>
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN73" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>36.8</t>
         </is>
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AQ73" t="inlineStr">
         <is>
-          <t>100.0599</t>
+          <t>98.3279</t>
         </is>
       </c>
       <c r="AR73" t="inlineStr">
         <is>
-          <t>0.434</t>
+          <t>0.432</t>
         </is>
       </c>
       <c r="AS73" t="inlineStr">
         <is>
-          <t>0.157</t>
+          <t>0.166</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr">
         <is>
-          <t>0.338</t>
+          <t>0.357</t>
         </is>
       </c>
       <c r="AU73" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="AV73" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>37.2</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>35.5</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>0.143</t>
         </is>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>7.16</t>
         </is>
       </c>
       <c r="BB73" t="inlineStr">
         <is>
-          <t>37.6</t>
+          <t>36.7</t>
         </is>
       </c>
       <c r="BC73" t="inlineStr">
         <is>
-          <t>87.9</t>
+          <t>88.83</t>
         </is>
       </c>
       <c r="BD73" t="inlineStr">
         <is>
-          <t>0.411</t>
+          <t>0.3769</t>
         </is>
       </c>
       <c r="BE73" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.1512</t>
         </is>
       </c>
       <c r="BF73" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="BG73" t="inlineStr"/>
       <c r="BH73" t="inlineStr"/>
       <c r="BI73" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>T-Mobile Park</t>
         </is>
       </c>
       <c r="BJ73" t="inlineStr"/>
@@ -20607,12 +20607,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>805808</t>
+          <t>679529</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Kevin McGonigle</t>
+          <t>Spencer Torkelson</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -20637,7 +20637,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -20656,7 +20656,7 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>46</v>
+        <v>45.9</v>
       </c>
       <c r="M74" t="inlineStr">
         <is>
@@ -20670,11 +20670,11 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel</t>
         </is>
       </c>
       <c r="P74" t="n">
-        <v>32.4</v>
+        <v>49.8</v>
       </c>
       <c r="Q74" t="n">
         <v>36.5</v>
@@ -20683,13 +20683,13 @@
         <v>25.4</v>
       </c>
       <c r="S74" t="n">
-        <v>88.7</v>
+        <v>71.7</v>
       </c>
       <c r="T74" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U74" t="n">
-        <v>61.5</v>
+        <v>47.2</v>
       </c>
       <c r="V74" t="inlineStr">
         <is>
@@ -20703,7 +20703,7 @@
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y74" t="inlineStr">
@@ -20728,7 +20728,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD74" t="inlineStr"/>
@@ -20745,27 +20745,27 @@
       </c>
       <c r="AH74" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI74" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK74" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 10/32, 1 HR</t>
         </is>
       </c>
       <c r="AL74" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.2% barrel, 13.5 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.2% barrel, 13.5 HR allowed</t>
         </is>
       </c>
       <c r="AM74" t="inlineStr">
@@ -20775,67 +20775,67 @@
       </c>
       <c r="AN74" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>13.22</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>36.8</t>
+          <t>42.58</t>
         </is>
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>89.78</t>
         </is>
       </c>
       <c r="AQ74" t="inlineStr">
         <is>
-          <t>98.3279</t>
+          <t>100.3127</t>
         </is>
       </c>
       <c r="AR74" t="inlineStr">
         <is>
-          <t>0.432</t>
+          <t>0.4238</t>
         </is>
       </c>
       <c r="AS74" t="inlineStr">
         <is>
-          <t>0.166</t>
+          <t>0.2027</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>0.3207</t>
         </is>
       </c>
       <c r="AU74" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>73.14</t>
         </is>
       </c>
       <c r="AV74" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>26.09</t>
         </is>
       </c>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>37.2</t>
+          <t>47.98</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>35.5</t>
+          <t>36.74</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>23.3</t>
         </is>
       </c>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>0.143</t>
+          <t>0.2083</t>
         </is>
       </c>
       <c r="BA74" t="inlineStr">
@@ -24062,7 +24062,7 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ86" t="inlineStr">
@@ -24072,7 +24072,7 @@
       </c>
       <c r="AK86" t="inlineStr">
         <is>
-          <t>Contact streak: 8/16 over last 7 games</t>
+          <t>Contact streak: 8/18 over last 7 games</t>
         </is>
       </c>
       <c r="AL86" t="inlineStr">
@@ -27783,27 +27783,27 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>630105</t>
+          <t>687093</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Jake Cronenworth</t>
+          <t>Vaughn Grissom</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-08-07T01:40:00Z</t>
+          <t>2026-08-06T16:35:00Z</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -27813,26 +27813,26 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Kohl Drake</t>
+          <t>Brandon Young</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>684442</t>
+          <t>687064</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L100" t="n">
-        <v>43.3</v>
+        <v>43.2</v>
       </c>
       <c r="M100" t="inlineStr">
         <is>
@@ -27846,26 +27846,26 @@
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>Projected Lineup, Pitcher Vulnerable</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P100" t="n">
-        <v>18.1</v>
+        <v>31.4</v>
       </c>
       <c r="Q100" t="n">
-        <v>86.09999999999999</v>
+        <v>41.8</v>
       </c>
       <c r="R100" t="n">
-        <v>28.2</v>
+        <v>32.1</v>
       </c>
       <c r="S100" t="n">
-        <v>47.9</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T100" t="n">
         <v>50</v>
       </c>
       <c r="U100" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="V100" t="inlineStr">
         <is>
@@ -27879,7 +27879,7 @@
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y100" t="inlineStr">
@@ -27904,7 +27904,7 @@
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD100" t="inlineStr"/>
@@ -27921,7 +27921,7 @@
       </c>
       <c r="AH100" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI100" t="inlineStr">
@@ -27936,119 +27936,119 @@
       </c>
       <c r="AK100" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/25, 0 HR</t>
+          <t>Last 7 games: 6/25, 0 HR</t>
         </is>
       </c>
       <c r="AL100" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 15.0% barrel, 3.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.5% barrel, 11.3 HR allowed</t>
         </is>
       </c>
       <c r="AM100" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN100" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="AO100" t="inlineStr">
         <is>
-          <t>34.17</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="AP100" t="inlineStr">
         <is>
-          <t>87.87</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AQ100" t="inlineStr">
         <is>
-          <t>98.2836</t>
+          <t>99.7602</t>
         </is>
       </c>
       <c r="AR100" t="inlineStr">
         <is>
-          <t>0.3397</t>
+          <t>0.409</t>
         </is>
       </c>
       <c r="AS100" t="inlineStr">
         <is>
-          <t>0.1077</t>
+          <t>0.148</t>
         </is>
       </c>
       <c r="AT100" t="inlineStr">
         <is>
-          <t>0.3036</t>
+          <t>0.329</t>
         </is>
       </c>
       <c r="AU100" t="inlineStr">
         <is>
-          <t>71.46</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="AV100" t="inlineStr">
         <is>
-          <t>17.81</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>32.24</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>0.0869</t>
+          <t>0.147</t>
         </is>
       </c>
       <c r="BA100" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>7.54</t>
         </is>
       </c>
       <c r="BB100" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>41.71</t>
         </is>
       </c>
       <c r="BC100" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>89.4</t>
         </is>
       </c>
       <c r="BD100" t="inlineStr">
         <is>
-          <t>0.594</t>
+          <t>0.4159</t>
         </is>
       </c>
       <c r="BE100" t="inlineStr">
         <is>
-          <t>0.295</t>
+          <t>0.163</t>
         </is>
       </c>
       <c r="BF100" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>27.71</t>
         </is>
       </c>
       <c r="BG100" t="inlineStr"/>
       <c r="BH100" t="inlineStr"/>
       <c r="BI100" t="inlineStr">
         <is>
-          <t>Chase Field</t>
+          <t>Oriole Park at Camden Yards</t>
         </is>
       </c>
       <c r="BJ100" t="inlineStr"/>
@@ -28059,27 +28059,27 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>687093</t>
+          <t>650402</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Vaughn Grissom</t>
+          <t>Gleyber Torres</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-08-06T16:35:00Z</t>
+          <t>2026-08-06T20:10:00Z</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -28089,17 +28089,17 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Brandon Young</t>
+          <t>Bryce Miller</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>687064</t>
+          <t>682243</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -28108,7 +28108,7 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>43.2</v>
+        <v>43</v>
       </c>
       <c r="M101" t="inlineStr">
         <is>
@@ -28122,26 +28122,26 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Premium Lineup Spot, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P101" t="n">
-        <v>31.4</v>
+        <v>26.4</v>
       </c>
       <c r="Q101" t="n">
-        <v>41.8</v>
+        <v>36.5</v>
       </c>
       <c r="R101" t="n">
-        <v>32.1</v>
+        <v>25.4</v>
       </c>
       <c r="S101" t="n">
-        <v>90.40000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="T101" t="n">
         <v>50</v>
       </c>
       <c r="U101" t="n">
-        <v>18</v>
+        <v>77</v>
       </c>
       <c r="V101" t="inlineStr">
         <is>
@@ -28155,7 +28155,7 @@
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y101" t="inlineStr">
@@ -28180,7 +28180,7 @@
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD101" t="inlineStr"/>
@@ -28197,134 +28197,134 @@
       </c>
       <c r="AH101" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI101" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/25, 0 HR</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL101" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.5% barrel, 11.3 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.2% barrel, 13.5 HR allowed</t>
         </is>
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN101" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>7.71</t>
         </is>
       </c>
       <c r="AO101" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>35.01</t>
         </is>
       </c>
       <c r="AP101" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>87.27</t>
         </is>
       </c>
       <c r="AQ101" t="inlineStr">
         <is>
-          <t>99.7602</t>
+          <t>97.7525</t>
         </is>
       </c>
       <c r="AR101" t="inlineStr">
         <is>
-          <t>0.409</t>
+          <t>0.4018</t>
         </is>
       </c>
       <c r="AS101" t="inlineStr">
         <is>
-          <t>0.148</t>
+          <t>0.1489</t>
         </is>
       </c>
       <c r="AT101" t="inlineStr">
         <is>
-          <t>0.329</t>
+          <t>0.3434</t>
         </is>
       </c>
       <c r="AU101" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>68.63</t>
         </is>
       </c>
       <c r="AV101" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>5.68</t>
         </is>
       </c>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>24.73</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>28.08</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>0.138</t>
         </is>
       </c>
       <c r="BA101" t="inlineStr">
         <is>
-          <t>7.54</t>
+          <t>7.16</t>
         </is>
       </c>
       <c r="BB101" t="inlineStr">
         <is>
-          <t>41.71</t>
+          <t>36.7</t>
         </is>
       </c>
       <c r="BC101" t="inlineStr">
         <is>
-          <t>89.4</t>
+          <t>88.83</t>
         </is>
       </c>
       <c r="BD101" t="inlineStr">
         <is>
-          <t>0.4159</t>
+          <t>0.3769</t>
         </is>
       </c>
       <c r="BE101" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>0.1512</t>
         </is>
       </c>
       <c r="BF101" t="inlineStr">
         <is>
-          <t>27.71</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="BG101" t="inlineStr"/>
       <c r="BH101" t="inlineStr"/>
       <c r="BI101" t="inlineStr">
         <is>
-          <t>Oriole Park at Camden Yards</t>
+          <t>T-Mobile Park</t>
         </is>
       </c>
       <c r="BJ101" t="inlineStr"/>
@@ -28335,27 +28335,27 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>650402</t>
+          <t>630105</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Gleyber Torres</t>
+          <t>Jake Cronenworth</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-08-06T20:10:00Z</t>
+          <t>2026-08-07T01:40:00Z</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -28365,26 +28365,26 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Bryce Miller</t>
+          <t>Kohl Drake</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>682243</t>
+          <t>684442</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L102" t="n">
-        <v>43.1</v>
+        <v>43</v>
       </c>
       <c r="M102" t="inlineStr">
         <is>
@@ -28398,26 +28398,26 @@
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Pitcher Vulnerable</t>
         </is>
       </c>
       <c r="P102" t="n">
-        <v>26.4</v>
+        <v>18.1</v>
       </c>
       <c r="Q102" t="n">
-        <v>36.5</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="R102" t="n">
-        <v>25.4</v>
+        <v>28.2</v>
       </c>
       <c r="S102" t="n">
-        <v>95.5</v>
+        <v>47.9</v>
       </c>
       <c r="T102" t="n">
         <v>50</v>
       </c>
       <c r="U102" t="n">
-        <v>78.40000000000001</v>
+        <v>19.5</v>
       </c>
       <c r="V102" t="inlineStr">
         <is>
@@ -28431,7 +28431,7 @@
       </c>
       <c r="X102" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y102" t="inlineStr">
@@ -28456,7 +28456,7 @@
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD102" t="inlineStr"/>
@@ -28473,27 +28473,27 @@
       </c>
       <c r="AH102" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI102" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Last 7 games: 7/28, 0 HR</t>
         </is>
       </c>
       <c r="AL102" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.2% barrel, 13.5 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 15.0% barrel, 3.0 HR allowed</t>
         </is>
       </c>
       <c r="AM102" t="inlineStr">
@@ -28503,104 +28503,104 @@
       </c>
       <c r="AN102" t="inlineStr">
         <is>
-          <t>7.71</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="AO102" t="inlineStr">
         <is>
-          <t>35.01</t>
+          <t>34.17</t>
         </is>
       </c>
       <c r="AP102" t="inlineStr">
         <is>
-          <t>87.27</t>
+          <t>87.87</t>
         </is>
       </c>
       <c r="AQ102" t="inlineStr">
         <is>
-          <t>97.7525</t>
+          <t>98.2836</t>
         </is>
       </c>
       <c r="AR102" t="inlineStr">
         <is>
-          <t>0.4018</t>
+          <t>0.3397</t>
         </is>
       </c>
       <c r="AS102" t="inlineStr">
         <is>
-          <t>0.1489</t>
+          <t>0.1077</t>
         </is>
       </c>
       <c r="AT102" t="inlineStr">
         <is>
-          <t>0.3434</t>
+          <t>0.3036</t>
         </is>
       </c>
       <c r="AU102" t="inlineStr">
         <is>
-          <t>68.63</t>
+          <t>71.46</t>
         </is>
       </c>
       <c r="AV102" t="inlineStr">
         <is>
-          <t>5.68</t>
+          <t>17.81</t>
         </is>
       </c>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>24.73</t>
+          <t>32.24</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>28.08</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>0.138</t>
+          <t>0.0869</t>
         </is>
       </c>
       <c r="BA102" t="inlineStr">
         <is>
-          <t>7.16</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="BB102" t="inlineStr">
         <is>
-          <t>36.7</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="BC102" t="inlineStr">
         <is>
-          <t>88.83</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="BD102" t="inlineStr">
         <is>
-          <t>0.3769</t>
+          <t>0.594</t>
         </is>
       </c>
       <c r="BE102" t="inlineStr">
         <is>
-          <t>0.1512</t>
+          <t>0.295</t>
         </is>
       </c>
       <c r="BF102" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="BG102" t="inlineStr"/>
       <c r="BH102" t="inlineStr"/>
       <c r="BI102" t="inlineStr">
         <is>
-          <t>T-Mobile Park</t>
+          <t>Chase Field</t>
         </is>
       </c>
       <c r="BJ102" t="inlineStr"/>
@@ -31144,7 +31144,7 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>41.2</v>
+        <v>41</v>
       </c>
       <c r="M112" t="inlineStr">
         <is>
@@ -31177,7 +31177,7 @@
         <v>50</v>
       </c>
       <c r="U112" t="n">
-        <v>63.3</v>
+        <v>59.3</v>
       </c>
       <c r="V112" t="inlineStr">
         <is>
@@ -31238,7 +31238,7 @@
       </c>
       <c r="AI112" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ112" t="inlineStr">
@@ -31248,7 +31248,7 @@
       </c>
       <c r="AK112" t="inlineStr">
         <is>
-          <t>Contact streak: 11/26 over last 7 games</t>
+          <t>Contact streak: 11/28 over last 7 games</t>
         </is>
       </c>
       <c r="AL112" t="inlineStr">
@@ -31923,27 +31923,27 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>645277</t>
+          <t>703601</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Ozzie Albies</t>
+          <t>Max Clark</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-08-06T23:15:00Z</t>
+          <t>2026-08-06T20:10:00Z</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -31953,17 +31953,17 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Janson Junk</t>
+          <t>Bryce Miller</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>676083</t>
+          <t>682243</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -31990,22 +31990,22 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>17.3</v>
+        <v>28.5</v>
       </c>
       <c r="Q115" t="n">
-        <v>41.4</v>
+        <v>36.5</v>
       </c>
       <c r="R115" t="n">
-        <v>30.9</v>
+        <v>25.4</v>
       </c>
       <c r="S115" t="n">
-        <v>81.90000000000001</v>
+        <v>59.8</v>
       </c>
       <c r="T115" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U115" t="n">
-        <v>36.3</v>
+        <v>55.6</v>
       </c>
       <c r="V115" t="inlineStr">
         <is>
@@ -32019,7 +32019,7 @@
       </c>
       <c r="X115" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y115" t="inlineStr">
@@ -32044,7 +32044,7 @@
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD115" t="inlineStr"/>
@@ -32056,17 +32056,17 @@
       </c>
       <c r="AG115" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AH115" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AH115" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AI115" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ115" t="inlineStr">
@@ -32076,119 +32076,119 @@
       </c>
       <c r="AK115" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/25, 1 HR</t>
+          <t>Contact streak: 7/19 over last 5 games</t>
         </is>
       </c>
       <c r="AL115" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 7.5% barrel, 10.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.2% barrel, 13.5 HR allowed</t>
         </is>
       </c>
       <c r="AM115" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN115" t="inlineStr">
         <is>
-          <t>4.62</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO115" t="inlineStr">
         <is>
-          <t>29.23</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AP115" t="inlineStr">
         <is>
-          <t>87.01</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="AQ115" t="inlineStr">
         <is>
-          <t>96.8613</t>
+          <t>98.2349</t>
         </is>
       </c>
       <c r="AR115" t="inlineStr">
         <is>
-          <t>0.3639</t>
+          <t>0.392</t>
         </is>
       </c>
       <c r="AS115" t="inlineStr">
         <is>
-          <t>0.1272</t>
+          <t>0.119</t>
         </is>
       </c>
       <c r="AT115" t="inlineStr">
         <is>
-          <t>0.2885</t>
+          <t>0.368</t>
         </is>
       </c>
       <c r="AU115" t="inlineStr">
         <is>
-          <t>68.93</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="AV115" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>35.1</t>
         </is>
       </c>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>46.77</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>31.83</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>0.1614</t>
+          <t>0.313</t>
         </is>
       </c>
       <c r="BA115" t="inlineStr">
         <is>
-          <t>7.52</t>
+          <t>7.16</t>
         </is>
       </c>
       <c r="BB115" t="inlineStr">
         <is>
-          <t>42.82</t>
+          <t>36.7</t>
         </is>
       </c>
       <c r="BC115" t="inlineStr">
         <is>
-          <t>90.55</t>
+          <t>88.83</t>
         </is>
       </c>
       <c r="BD115" t="inlineStr">
         <is>
-          <t>0.4194</t>
+          <t>0.3769</t>
         </is>
       </c>
       <c r="BE115" t="inlineStr">
         <is>
-          <t>0.1599</t>
+          <t>0.1512</t>
         </is>
       </c>
       <c r="BF115" t="inlineStr">
         <is>
-          <t>23.57</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="BG115" t="inlineStr"/>
       <c r="BH115" t="inlineStr"/>
       <c r="BI115" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>T-Mobile Park</t>
         </is>
       </c>
       <c r="BJ115" t="inlineStr"/>
@@ -32199,27 +32199,27 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>703601</t>
+          <t>645277</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Max Clark</t>
+          <t>Ozzie Albies</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-08-06T20:10:00Z</t>
+          <t>2026-08-06T23:15:00Z</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -32229,17 +32229,17 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Bryce Miller</t>
+          <t>Janson Junk</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>682243</t>
+          <t>676083</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -32248,7 +32248,7 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>40.2</v>
+        <v>40.3</v>
       </c>
       <c r="M116" t="inlineStr">
         <is>
@@ -32266,22 +32266,22 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>28.5</v>
+        <v>17.3</v>
       </c>
       <c r="Q116" t="n">
-        <v>36.5</v>
+        <v>41.4</v>
       </c>
       <c r="R116" t="n">
-        <v>25.4</v>
+        <v>30.9</v>
       </c>
       <c r="S116" t="n">
-        <v>59.8</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T116" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U116" t="n">
-        <v>53.3</v>
+        <v>36.3</v>
       </c>
       <c r="V116" t="inlineStr">
         <is>
@@ -32295,7 +32295,7 @@
       </c>
       <c r="X116" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y116" t="inlineStr">
@@ -32320,7 +32320,7 @@
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD116" t="inlineStr"/>
@@ -32332,7 +32332,7 @@
       </c>
       <c r="AG116" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AH116" t="inlineStr">
@@ -32342,7 +32342,7 @@
       </c>
       <c r="AI116" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ116" t="inlineStr">
@@ -32352,119 +32352,119 @@
       </c>
       <c r="AK116" t="inlineStr">
         <is>
-          <t>Contact streak: 6/17 over last 5 games</t>
+          <t>Last 7 games: 6/25, 1 HR</t>
         </is>
       </c>
       <c r="AL116" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.2% barrel, 13.5 HR allowed</t>
+          <t>switch hitter; pitcher baseline 7.5% barrel, 10.1 HR allowed</t>
         </is>
       </c>
       <c r="AM116" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN116" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.62</t>
         </is>
       </c>
       <c r="AO116" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>29.23</t>
         </is>
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>87.01</t>
         </is>
       </c>
       <c r="AQ116" t="inlineStr">
         <is>
-          <t>98.2349</t>
+          <t>96.8613</t>
         </is>
       </c>
       <c r="AR116" t="inlineStr">
         <is>
-          <t>0.392</t>
+          <t>0.3639</t>
         </is>
       </c>
       <c r="AS116" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>0.1272</t>
         </is>
       </c>
       <c r="AT116" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>0.2885</t>
         </is>
       </c>
       <c r="AU116" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>68.93</t>
         </is>
       </c>
       <c r="AV116" t="inlineStr">
         <is>
-          <t>35.1</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>46.77</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>31.83</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>0.313</t>
+          <t>0.1614</t>
         </is>
       </c>
       <c r="BA116" t="inlineStr">
         <is>
-          <t>7.16</t>
+          <t>7.52</t>
         </is>
       </c>
       <c r="BB116" t="inlineStr">
         <is>
-          <t>36.7</t>
+          <t>42.82</t>
         </is>
       </c>
       <c r="BC116" t="inlineStr">
         <is>
-          <t>88.83</t>
+          <t>90.55</t>
         </is>
       </c>
       <c r="BD116" t="inlineStr">
         <is>
-          <t>0.3769</t>
+          <t>0.4194</t>
         </is>
       </c>
       <c r="BE116" t="inlineStr">
         <is>
-          <t>0.1512</t>
+          <t>0.1599</t>
         </is>
       </c>
       <c r="BF116" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>23.57</t>
         </is>
       </c>
       <c r="BG116" t="inlineStr"/>
       <c r="BH116" t="inlineStr"/>
       <c r="BI116" t="inlineStr">
         <is>
-          <t>T-Mobile Park</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ116" t="inlineStr"/>
@@ -36973,7 +36973,7 @@
         <v>50</v>
       </c>
       <c r="U133" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="V133" t="inlineStr">
         <is>
@@ -37034,7 +37034,7 @@
       </c>
       <c r="AI133" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ133" t="inlineStr">
@@ -37044,7 +37044,7 @@
       </c>
       <c r="AK133" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 0 HR</t>
+          <t>Last 7 games: 6/25, 0 HR</t>
         </is>
       </c>
       <c r="AL133" t="inlineStr">
@@ -37443,27 +37443,27 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>621493</t>
+          <t>643446</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Taylor Ward</t>
+          <t>Jeff McNeil</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-08-06T20:10:00Z</t>
+          <t>2026-08-06T16:40:00Z</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -37473,17 +37473,17 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Framber Valdez</t>
+          <t>Andrew Abbott</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>664285</t>
+          <t>671096</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -37492,7 +37492,7 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>37.1</v>
+        <v>37</v>
       </c>
       <c r="M135" t="inlineStr">
         <is>
@@ -37506,26 +37506,26 @@
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P135" t="n">
-        <v>32.3</v>
+        <v>12.2</v>
       </c>
       <c r="Q135" t="n">
-        <v>36.2</v>
+        <v>40.2</v>
       </c>
       <c r="R135" t="n">
-        <v>25.4</v>
+        <v>39.3</v>
       </c>
       <c r="S135" t="n">
-        <v>47.9</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T135" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U135" t="n">
-        <v>5.7</v>
+        <v>30</v>
       </c>
       <c r="V135" t="inlineStr">
         <is>
@@ -37539,7 +37539,7 @@
       </c>
       <c r="X135" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y135" t="inlineStr">
@@ -37581,12 +37581,12 @@
       </c>
       <c r="AH135" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI135" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ135" t="inlineStr">
@@ -37596,12 +37596,12 @@
       </c>
       <c r="AK135" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/19, 0 HR</t>
+          <t>Contact streak: 8/25 over last 7 games</t>
         </is>
       </c>
       <c r="AL135" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.4% barrel, 12.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.7% barrel, 17.6 HR allowed</t>
         </is>
       </c>
       <c r="AM135" t="inlineStr">
@@ -37611,104 +37611,104 @@
       </c>
       <c r="AN135" t="inlineStr">
         <is>
-          <t>7.96</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="AO135" t="inlineStr">
         <is>
-          <t>39.97</t>
+          <t>32.34</t>
         </is>
       </c>
       <c r="AP135" t="inlineStr">
         <is>
-          <t>89.4</t>
+          <t>86.64</t>
         </is>
       </c>
       <c r="AQ135" t="inlineStr">
         <is>
-          <t>99.5054</t>
+          <t>96.6961</t>
         </is>
       </c>
       <c r="AR135" t="inlineStr">
         <is>
-          <t>0.3975</t>
+          <t>0.3698</t>
         </is>
       </c>
       <c r="AS135" t="inlineStr">
         <is>
-          <t>0.1546</t>
+          <t>0.0978</t>
         </is>
       </c>
       <c r="AT135" t="inlineStr">
         <is>
-          <t>0.3414</t>
+          <t>0.3132</t>
         </is>
       </c>
       <c r="AU135" t="inlineStr">
         <is>
-          <t>68.73</t>
+          <t>69.02</t>
         </is>
       </c>
       <c r="AV135" t="inlineStr">
         <is>
-          <t>4.16</t>
+          <t>5.09</t>
         </is>
       </c>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>33.66</t>
+          <t>43.21</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>29.66</t>
+          <t>23.33</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr">
         <is>
-          <t>15.7</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>0.1434</t>
+          <t>0.1064</t>
         </is>
       </c>
       <c r="BA135" t="inlineStr">
         <is>
-          <t>6.42</t>
+          <t>7.65</t>
         </is>
       </c>
       <c r="BB135" t="inlineStr">
         <is>
-          <t>44.27</t>
+          <t>36.71</t>
         </is>
       </c>
       <c r="BC135" t="inlineStr">
         <is>
-          <t>90.17</t>
+          <t>89.06</t>
         </is>
       </c>
       <c r="BD135" t="inlineStr">
         <is>
-          <t>0.3847</t>
+          <t>0.4081</t>
         </is>
       </c>
       <c r="BE135" t="inlineStr">
         <is>
-          <t>0.1353</t>
+          <t>0.1597</t>
         </is>
       </c>
       <c r="BF135" t="inlineStr">
         <is>
-          <t>19.3</t>
+          <t>28.28</t>
         </is>
       </c>
       <c r="BG135" t="inlineStr"/>
       <c r="BH135" t="inlineStr"/>
       <c r="BI135" t="inlineStr">
         <is>
-          <t>T-Mobile Park</t>
+          <t>Great American Ball Park</t>
         </is>
       </c>
       <c r="BJ135" t="inlineStr"/>
@@ -37719,24 +37719,24 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>643446</t>
+          <t>680574</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Jeff McNeil</t>
+          <t>Matt McLain</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
+          <t>CIN</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
           <t>ATH</t>
         </is>
       </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>CIN</t>
-        </is>
-      </c>
       <c r="F136" t="inlineStr">
         <is>
           <t>2026-08-06T16:40:00Z</t>
@@ -37749,22 +37749,22 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Andrew Abbott</t>
+          <t>Mason Barnett</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>671096</t>
+          <t>686930</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L136" t="n">
@@ -37786,22 +37786,22 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>12.2</v>
+        <v>31.3</v>
       </c>
       <c r="Q136" t="n">
-        <v>40.2</v>
+        <v>38.5</v>
       </c>
       <c r="R136" t="n">
         <v>39.3</v>
       </c>
       <c r="S136" t="n">
-        <v>81.90000000000001</v>
+        <v>40.2</v>
       </c>
       <c r="T136" t="n">
         <v>50</v>
       </c>
       <c r="U136" t="n">
-        <v>30</v>
+        <v>28.9</v>
       </c>
       <c r="V136" t="inlineStr">
         <is>
@@ -37815,7 +37815,7 @@
       </c>
       <c r="X136" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y136" t="inlineStr">
@@ -37857,127 +37857,127 @@
       </c>
       <c r="AH136" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI136" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK136" t="inlineStr">
         <is>
-          <t>Contact streak: 8/25 over last 7 games</t>
+          <t>Last 7 games: 4/21, 1 HR</t>
         </is>
       </c>
       <c r="AL136" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.7% barrel, 17.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.3% barrel, 4.4 HR allowed</t>
         </is>
       </c>
       <c r="AM136" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN136" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>8.43</t>
         </is>
       </c>
       <c r="AO136" t="inlineStr">
         <is>
-          <t>32.34</t>
+          <t>37.55</t>
         </is>
       </c>
       <c r="AP136" t="inlineStr">
         <is>
-          <t>86.64</t>
+          <t>88.17</t>
         </is>
       </c>
       <c r="AQ136" t="inlineStr">
         <is>
-          <t>96.6961</t>
+          <t>98.8249</t>
         </is>
       </c>
       <c r="AR136" t="inlineStr">
         <is>
-          <t>0.3698</t>
+          <t>0.375</t>
         </is>
       </c>
       <c r="AS136" t="inlineStr">
         <is>
-          <t>0.0978</t>
+          <t>0.1511</t>
         </is>
       </c>
       <c r="AT136" t="inlineStr">
         <is>
-          <t>0.3132</t>
+          <t>0.3068</t>
         </is>
       </c>
       <c r="AU136" t="inlineStr">
         <is>
-          <t>69.02</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AV136" t="inlineStr">
         <is>
-          <t>5.09</t>
+          <t>10.24</t>
         </is>
       </c>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>43.21</t>
+          <t>33.54</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>23.33</t>
+          <t>32.24</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>0.1064</t>
+          <t>0.1307</t>
         </is>
       </c>
       <c r="BA136" t="inlineStr">
         <is>
-          <t>7.65</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="BB136" t="inlineStr">
         <is>
-          <t>36.71</t>
+          <t>39.42</t>
         </is>
       </c>
       <c r="BC136" t="inlineStr">
         <is>
-          <t>89.06</t>
+          <t>88.92</t>
         </is>
       </c>
       <c r="BD136" t="inlineStr">
         <is>
-          <t>0.4081</t>
+          <t>0.3787</t>
         </is>
       </c>
       <c r="BE136" t="inlineStr">
         <is>
-          <t>0.1597</t>
+          <t>0.1502</t>
         </is>
       </c>
       <c r="BF136" t="inlineStr">
         <is>
-          <t>28.28</t>
+          <t>31.13</t>
         </is>
       </c>
       <c r="BG136" t="inlineStr"/>
@@ -37995,27 +37995,27 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>680574</t>
+          <t>621493</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Matt McLain</t>
+          <t>Taylor Ward</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-08-06T16:40:00Z</t>
+          <t>2026-08-06T20:10:00Z</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -38025,22 +38025,22 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Mason Barnett</t>
+          <t>Framber Valdez</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>686930</t>
+          <t>664285</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L137" t="n">
@@ -38058,26 +38058,26 @@
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P137" t="n">
-        <v>31.3</v>
+        <v>32.3</v>
       </c>
       <c r="Q137" t="n">
-        <v>38.5</v>
+        <v>36.2</v>
       </c>
       <c r="R137" t="n">
-        <v>39.3</v>
+        <v>25.4</v>
       </c>
       <c r="S137" t="n">
-        <v>40.2</v>
+        <v>47.9</v>
       </c>
       <c r="T137" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U137" t="n">
-        <v>28.9</v>
+        <v>3.4</v>
       </c>
       <c r="V137" t="inlineStr">
         <is>
@@ -38091,7 +38091,7 @@
       </c>
       <c r="X137" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y137" t="inlineStr">
@@ -38133,7 +38133,7 @@
       </c>
       <c r="AH137" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI137" t="inlineStr">
@@ -38143,124 +38143,124 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 1 HR</t>
+          <t>Last 7 games: 3/21, 0 HR</t>
         </is>
       </c>
       <c r="AL137" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.3% barrel, 4.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.4% barrel, 12.9 HR allowed</t>
         </is>
       </c>
       <c r="AM137" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN137" t="inlineStr">
         <is>
-          <t>8.43</t>
+          <t>7.96</t>
         </is>
       </c>
       <c r="AO137" t="inlineStr">
         <is>
-          <t>37.55</t>
+          <t>39.97</t>
         </is>
       </c>
       <c r="AP137" t="inlineStr">
         <is>
-          <t>88.17</t>
+          <t>89.4</t>
         </is>
       </c>
       <c r="AQ137" t="inlineStr">
         <is>
-          <t>98.8249</t>
+          <t>99.5054</t>
         </is>
       </c>
       <c r="AR137" t="inlineStr">
         <is>
-          <t>0.375</t>
+          <t>0.3975</t>
         </is>
       </c>
       <c r="AS137" t="inlineStr">
         <is>
-          <t>0.1511</t>
+          <t>0.1546</t>
         </is>
       </c>
       <c r="AT137" t="inlineStr">
         <is>
-          <t>0.3068</t>
+          <t>0.3414</t>
         </is>
       </c>
       <c r="AU137" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>68.73</t>
         </is>
       </c>
       <c r="AV137" t="inlineStr">
         <is>
-          <t>10.24</t>
+          <t>4.16</t>
         </is>
       </c>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>33.54</t>
+          <t>33.66</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>32.24</t>
+          <t>29.66</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>15.7</t>
         </is>
       </c>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>0.1307</t>
+          <t>0.1434</t>
         </is>
       </c>
       <c r="BA137" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>6.42</t>
         </is>
       </c>
       <c r="BB137" t="inlineStr">
         <is>
-          <t>39.42</t>
+          <t>44.27</t>
         </is>
       </c>
       <c r="BC137" t="inlineStr">
         <is>
-          <t>88.92</t>
+          <t>90.17</t>
         </is>
       </c>
       <c r="BD137" t="inlineStr">
         <is>
-          <t>0.3787</t>
+          <t>0.3847</t>
         </is>
       </c>
       <c r="BE137" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.1353</t>
         </is>
       </c>
       <c r="BF137" t="inlineStr">
         <is>
-          <t>31.13</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="BG137" t="inlineStr"/>
       <c r="BH137" t="inlineStr"/>
       <c r="BI137" t="inlineStr">
         <is>
-          <t>Great American Ball Park</t>
+          <t>T-Mobile Park</t>
         </is>
       </c>
       <c r="BJ137" t="inlineStr"/>
@@ -45220,7 +45220,7 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>33.1</v>
+        <v>32.9</v>
       </c>
       <c r="M163" t="inlineStr">
         <is>
@@ -45253,7 +45253,7 @@
         <v>50</v>
       </c>
       <c r="U163" t="n">
-        <v>21.1</v>
+        <v>18</v>
       </c>
       <c r="V163" t="inlineStr">
         <is>
@@ -45314,7 +45314,7 @@
       </c>
       <c r="AI163" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ163" t="inlineStr">
@@ -45324,7 +45324,7 @@
       </c>
       <c r="AK163" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/23, 0 HR</t>
+          <t>Last 7 games: 6/25, 0 HR</t>
         </is>
       </c>
       <c r="AL163" t="inlineStr">
@@ -50967,27 +50967,27 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>669221</t>
+          <t>806068</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Sean Murphy</t>
+          <t>Colt Emerson</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>2026-08-06T23:15:00Z</t>
+          <t>2026-08-06T20:10:00Z</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
@@ -51002,21 +51002,21 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>Janson Junk</t>
+          <t>Framber Valdez</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>676083</t>
+          <t>664285</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L184" t="n">
-        <v>27.2</v>
+        <v>27.9</v>
       </c>
       <c r="M184" t="inlineStr">
         <is>
@@ -51034,13 +51034,13 @@
         </is>
       </c>
       <c r="P184" t="n">
-        <v>6.8</v>
+        <v>12</v>
       </c>
       <c r="Q184" t="n">
-        <v>42.5</v>
+        <v>36.2</v>
       </c>
       <c r="R184" t="n">
-        <v>30.9</v>
+        <v>25.4</v>
       </c>
       <c r="S184" t="n">
         <v>40.2</v>
@@ -51049,7 +51049,7 @@
         <v>50</v>
       </c>
       <c r="U184" t="n">
-        <v>0</v>
+        <v>26.4</v>
       </c>
       <c r="V184" t="inlineStr">
         <is>
@@ -51088,7 +51088,7 @@
       </c>
       <c r="AC184" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD184" t="inlineStr"/>
@@ -51100,32 +51100,32 @@
       </c>
       <c r="AG184" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AH184" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI184" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK184" t="inlineStr">
         <is>
-          <t>Last 5 games: 2/18, 0 HR</t>
+          <t>Last 7 games: 4/23, 1 HR</t>
         </is>
       </c>
       <c r="AL184" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.5% barrel, 10.1 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.4% barrel, 12.9 HR allowed</t>
         </is>
       </c>
       <c r="AM184" t="inlineStr">
@@ -51135,104 +51135,104 @@
       </c>
       <c r="AN184" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="AO184" t="inlineStr">
         <is>
-          <t>30.43</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="AP184" t="inlineStr">
         <is>
-          <t>82.94</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AQ184" t="inlineStr">
         <is>
-          <t>98.84</t>
+          <t>96.4597</t>
         </is>
       </c>
       <c r="AR184" t="inlineStr">
         <is>
-          <t>0.2344</t>
+          <t>0.289</t>
         </is>
       </c>
       <c r="AS184" t="inlineStr">
         <is>
-          <t>0.0761</t>
+          <t>0.098</t>
         </is>
       </c>
       <c r="AT184" t="inlineStr">
         <is>
-          <t>0.1873</t>
+          <t>0.246</t>
         </is>
       </c>
       <c r="AU184" t="inlineStr">
         <is>
-          <t>68.96</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AV184" t="inlineStr">
         <is>
-          <t>15.52</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>49.61</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>26.56</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AZ184" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>0.146</t>
         </is>
       </c>
       <c r="BA184" t="inlineStr">
         <is>
-          <t>7.52</t>
+          <t>6.42</t>
         </is>
       </c>
       <c r="BB184" t="inlineStr">
         <is>
-          <t>42.82</t>
+          <t>44.27</t>
         </is>
       </c>
       <c r="BC184" t="inlineStr">
         <is>
-          <t>90.55</t>
+          <t>90.17</t>
         </is>
       </c>
       <c r="BD184" t="inlineStr">
         <is>
-          <t>0.4194</t>
+          <t>0.3847</t>
         </is>
       </c>
       <c r="BE184" t="inlineStr">
         <is>
-          <t>0.1599</t>
+          <t>0.1353</t>
         </is>
       </c>
       <c r="BF184" t="inlineStr">
         <is>
-          <t>23.57</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="BG184" t="inlineStr"/>
       <c r="BH184" t="inlineStr"/>
       <c r="BI184" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>T-Mobile Park</t>
         </is>
       </c>
       <c r="BJ184" t="inlineStr"/>
@@ -51243,27 +51243,27 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>805367</t>
+          <t>669221</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Chase Meidroth</t>
+          <t>Sean Murphy</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>2026-08-06T23:10:00Z</t>
+          <t>2026-08-06T23:15:00Z</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
@@ -51273,26 +51273,26 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>Ranger Suarez</t>
+          <t>Janson Junk</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>624133</t>
+          <t>676083</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L185" t="n">
-        <v>26.8</v>
+        <v>27.2</v>
       </c>
       <c r="M185" t="inlineStr">
         <is>
@@ -51306,26 +51306,26 @@
       </c>
       <c r="O185" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P185" t="n">
-        <v>13</v>
+        <v>6.8</v>
       </c>
       <c r="Q185" t="n">
-        <v>16.6</v>
+        <v>42.5</v>
       </c>
       <c r="R185" t="n">
-        <v>28.7</v>
+        <v>30.9</v>
       </c>
       <c r="S185" t="n">
-        <v>47.9</v>
+        <v>40.2</v>
       </c>
       <c r="T185" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U185" t="n">
-        <v>10.6</v>
+        <v>0</v>
       </c>
       <c r="V185" t="inlineStr">
         <is>
@@ -51339,7 +51339,7 @@
       </c>
       <c r="X185" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y185" t="inlineStr">
@@ -51376,17 +51376,17 @@
       </c>
       <c r="AG185" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AH185" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI185" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ185" t="inlineStr">
@@ -51396,12 +51396,12 @@
       </c>
       <c r="AK185" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 0 HR</t>
+          <t>Last 5 games: 2/18, 0 HR</t>
         </is>
       </c>
       <c r="AL185" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.9% barrel, 7.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.5% barrel, 10.1 HR allowed</t>
         </is>
       </c>
       <c r="AM185" t="inlineStr">
@@ -51411,104 +51411,104 @@
       </c>
       <c r="AN185" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>4.02</t>
         </is>
       </c>
       <c r="AO185" t="inlineStr">
         <is>
-          <t>35.12</t>
+          <t>30.43</t>
         </is>
       </c>
       <c r="AP185" t="inlineStr">
         <is>
-          <t>88.06</t>
+          <t>82.94</t>
         </is>
       </c>
       <c r="AQ185" t="inlineStr">
         <is>
-          <t>97.4521</t>
+          <t>98.84</t>
         </is>
       </c>
       <c r="AR185" t="inlineStr">
         <is>
-          <t>0.3323</t>
+          <t>0.2344</t>
         </is>
       </c>
       <c r="AS185" t="inlineStr">
         <is>
-          <t>0.0933</t>
+          <t>0.0761</t>
         </is>
       </c>
       <c r="AT185" t="inlineStr">
         <is>
-          <t>0.2951</t>
+          <t>0.1873</t>
         </is>
       </c>
       <c r="AU185" t="inlineStr">
         <is>
-          <t>67.19</t>
+          <t>68.96</t>
         </is>
       </c>
       <c r="AV185" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>15.52</t>
         </is>
       </c>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>37.42</t>
+          <t>49.61</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>19.56</t>
+          <t>26.56</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="AZ185" t="inlineStr">
         <is>
-          <t>0.1027</t>
+          <t>0.063</t>
         </is>
       </c>
       <c r="BA185" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>7.52</t>
         </is>
       </c>
       <c r="BB185" t="inlineStr">
         <is>
-          <t>32.57</t>
+          <t>42.82</t>
         </is>
       </c>
       <c r="BC185" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>90.55</t>
         </is>
       </c>
       <c r="BD185" t="inlineStr">
         <is>
-          <t>0.3447</t>
+          <t>0.4194</t>
         </is>
       </c>
       <c r="BE185" t="inlineStr">
         <is>
-          <t>0.1068</t>
+          <t>0.1599</t>
         </is>
       </c>
       <c r="BF185" t="inlineStr">
         <is>
-          <t>22.49</t>
+          <t>23.57</t>
         </is>
       </c>
       <c r="BG185" t="inlineStr"/>
       <c r="BH185" t="inlineStr"/>
       <c r="BI185" t="inlineStr">
         <is>
-          <t>Fenway Park</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ185" t="inlineStr"/>
@@ -51519,27 +51519,27 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>806068</t>
+          <t>805367</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Colt Emerson</t>
+          <t>Chase Meidroth</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>2026-08-06T20:10:00Z</t>
+          <t>2026-08-06T23:10:00Z</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
@@ -51549,17 +51549,17 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>Framber Valdez</t>
+          <t>Ranger Suarez</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>664285</t>
+          <t>624133</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
@@ -51568,7 +51568,7 @@
         </is>
       </c>
       <c r="L186" t="n">
-        <v>26.7</v>
+        <v>26.8</v>
       </c>
       <c r="M186" t="inlineStr">
         <is>
@@ -51582,26 +51582,26 @@
       </c>
       <c r="O186" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P186" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q186" t="n">
-        <v>36.2</v>
+        <v>16.6</v>
       </c>
       <c r="R186" t="n">
-        <v>25.4</v>
+        <v>28.7</v>
       </c>
       <c r="S186" t="n">
-        <v>40.2</v>
+        <v>47.9</v>
       </c>
       <c r="T186" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U186" t="n">
-        <v>3.4</v>
+        <v>10.6</v>
       </c>
       <c r="V186" t="inlineStr">
         <is>
@@ -51615,7 +51615,7 @@
       </c>
       <c r="X186" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y186" t="inlineStr">
@@ -51640,7 +51640,7 @@
       </c>
       <c r="AC186" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD186" t="inlineStr"/>
@@ -51657,7 +51657,7 @@
       </c>
       <c r="AH186" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI186" t="inlineStr">
@@ -51672,12 +51672,12 @@
       </c>
       <c r="AK186" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/21, 0 HR</t>
+          <t>Last 7 games: 4/21, 0 HR</t>
         </is>
       </c>
       <c r="AL186" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.4% barrel, 12.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.9% barrel, 7.7 HR allowed</t>
         </is>
       </c>
       <c r="AM186" t="inlineStr">
@@ -51687,104 +51687,104 @@
       </c>
       <c r="AN186" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="AO186" t="inlineStr">
         <is>
-          <t>28.7</t>
+          <t>35.12</t>
         </is>
       </c>
       <c r="AP186" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>88.06</t>
         </is>
       </c>
       <c r="AQ186" t="inlineStr">
         <is>
-          <t>96.4597</t>
+          <t>97.4521</t>
         </is>
       </c>
       <c r="AR186" t="inlineStr">
         <is>
-          <t>0.289</t>
+          <t>0.3323</t>
         </is>
       </c>
       <c r="AS186" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>0.0933</t>
         </is>
       </c>
       <c r="AT186" t="inlineStr">
         <is>
-          <t>0.246</t>
+          <t>0.2951</t>
         </is>
       </c>
       <c r="AU186" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>67.19</t>
         </is>
       </c>
       <c r="AV186" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>37.42</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>19.56</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="AZ186" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>0.1027</t>
         </is>
       </c>
       <c r="BA186" t="inlineStr">
         <is>
-          <t>6.42</t>
+          <t>4.94</t>
         </is>
       </c>
       <c r="BB186" t="inlineStr">
         <is>
-          <t>44.27</t>
+          <t>32.57</t>
         </is>
       </c>
       <c r="BC186" t="inlineStr">
         <is>
-          <t>90.17</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="BD186" t="inlineStr">
         <is>
-          <t>0.3847</t>
+          <t>0.3447</t>
         </is>
       </c>
       <c r="BE186" t="inlineStr">
         <is>
-          <t>0.1353</t>
+          <t>0.1068</t>
         </is>
       </c>
       <c r="BF186" t="inlineStr">
         <is>
-          <t>19.3</t>
+          <t>22.49</t>
         </is>
       </c>
       <c r="BG186" t="inlineStr"/>
       <c r="BH186" t="inlineStr"/>
       <c r="BI186" t="inlineStr">
         <is>
-          <t>T-Mobile Park</t>
+          <t>Fenway Park</t>
         </is>
       </c>
       <c r="BJ186" t="inlineStr"/>
@@ -53705,12 +53705,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>592518</t>
+          <t>665487</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Manny Machado</t>
+          <t>Fernando Tatis</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -53735,7 +53735,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -53754,7 +53754,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>61.9</v>
+        <v>62.4</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -53772,7 +53772,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>50.9</v>
+        <v>50.2</v>
       </c>
       <c r="Q4" t="n">
         <v>86.09999999999999</v>
@@ -53781,13 +53781,13 @@
         <v>28.2</v>
       </c>
       <c r="S4" t="n">
-        <v>92.09999999999999</v>
+        <v>88.7</v>
       </c>
       <c r="T4" t="n">
         <v>78</v>
       </c>
       <c r="U4" t="n">
-        <v>6</v>
+        <v>29.2</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
@@ -53801,7 +53801,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -53843,22 +53843,22 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/25, 0 HR</t>
+          <t>Last 7 games: 5/26, 1 HR</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -53868,72 +53868,72 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>EV profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>11.43</t>
+          <t>10.58</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>46.53</t>
+          <t>52.43</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>91.29</t>
+          <t>92.46</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>101.9072</t>
+          <t>104.2761</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.4495</t>
+          <t>0.4516</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.203</t>
+          <t>0.1708</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.3347</t>
+          <t>0.3574</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>74.64</t>
+          <t>75.44</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>44.51</t>
+          <t>57.35</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>40.92</t>
+          <t>33.68</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>28.99</t>
+          <t>21.31</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.2067</t>
+          <t>0.1346</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
@@ -53981,12 +53981,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>664034</t>
+          <t>592518</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ty France</t>
+          <t>Manny Machado</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -54011,7 +54011,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -54030,7 +54030,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>61.4</v>
+        <v>61.8</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -54048,7 +54048,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>45.7</v>
+        <v>50.9</v>
       </c>
       <c r="Q5" t="n">
         <v>86.09999999999999</v>
@@ -54057,13 +54057,13 @@
         <v>28.2</v>
       </c>
       <c r="S5" t="n">
-        <v>90.40000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T5" t="n">
         <v>78</v>
       </c>
       <c r="U5" t="n">
-        <v>34.2</v>
+        <v>5.1</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -54077,7 +54077,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -54119,12 +54119,12 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -54134,7 +54134,7 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Contact streak: 8/23 over last 7 games</t>
+          <t>Last 7 games: 4/26, 0 HR</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -54149,67 +54149,67 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>10.01</t>
+          <t>11.43</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>48.61</t>
+          <t>46.53</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>91.67</t>
+          <t>91.29</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>101.4652</t>
+          <t>101.9072</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.439</t>
+          <t>0.4495</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.1828</t>
+          <t>0.203</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.3315</t>
+          <t>0.3347</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>74.64</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>18.76</t>
+          <t>44.51</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>36.15</t>
+          <t>40.92</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>24.27</t>
+          <t>28.99</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.1947</t>
+          <t>0.2067</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
@@ -54257,12 +54257,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>665487</t>
+          <t>664034</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Fernando Tatis</t>
+          <t>Ty France</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -54287,7 +54287,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -54324,7 +54324,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>50.2</v>
+        <v>45.7</v>
       </c>
       <c r="Q6" t="n">
         <v>86.09999999999999</v>
@@ -54333,13 +54333,13 @@
         <v>28.2</v>
       </c>
       <c r="S6" t="n">
-        <v>88.7</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T6" t="n">
         <v>78</v>
       </c>
       <c r="U6" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -54353,7 +54353,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -54395,12 +54395,12 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -54410,7 +54410,7 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 0 HR</t>
+          <t>Contact streak: 8/25 over last 7 games</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -54420,72 +54420,72 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>EV profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>10.58</t>
+          <t>10.01</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>52.43</t>
+          <t>48.61</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>92.46</t>
+          <t>91.67</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>104.2761</t>
+          <t>101.4652</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.4516</t>
+          <t>0.439</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.1708</t>
+          <t>0.1828</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3574</t>
+          <t>0.3315</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>75.44</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>57.35</t>
+          <t>18.76</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>33.68</t>
+          <t>36.15</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>21.31</t>
+          <t>24.27</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.1346</t>
+          <t>0.1947</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -55410,7 +55410,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>58.9</v>
+        <v>58.8</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -55443,7 +55443,7 @@
         <v>50</v>
       </c>
       <c r="U10" t="n">
-        <v>46.5</v>
+        <v>44.8</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -55504,7 +55504,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -55514,7 +55514,7 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/26, 1 HR</t>
+          <t>Last 7 games: 8/27, 1 HR</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
